--- a/data/restaurants.xlsx
+++ b/data/restaurants.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\woody\Documents\AI_개발\my-restaurant-map\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6795DE6A-055A-4CC7-A4DC-197ABEEC38F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0E1F22F-CDAC-43C5-9673-39A93C74CA98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="270" yWindow="720" windowWidth="27585" windowHeight="15285" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="120">
   <si>
     <t>id</t>
   </si>
@@ -55,9 +55,6 @@
     <t>1</t>
   </si>
   <si>
-    <t>굿푸드</t>
-  </si>
-  <si>
     <t>서울특별시 구로구 디지털로26길 5</t>
   </si>
   <si>
@@ -398,6 +395,10 @@
   </si>
   <si>
     <t xml:space="preserve"> </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>굿푸드(구로점)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -856,7 +857,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>2</v>
@@ -888,242 +889,242 @@
         <v>10</v>
       </c>
       <c r="B2" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="D2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="D2" s="4" t="s">
+      <c r="E2" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="F2" s="8" t="s">
         <v>13</v>
-      </c>
-      <c r="F2" s="8" t="s">
-        <v>14</v>
       </c>
       <c r="G2" s="4"/>
       <c r="H2" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="I2" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="J2" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="J2" s="4" t="s">
+      <c r="K2" s="4" t="s">
         <v>17</v>
-      </c>
-      <c r="K2" s="4" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="C3" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="E3" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="E3" s="8" t="s">
+      <c r="F3" s="8" t="s">
         <v>21</v>
-      </c>
-      <c r="F3" s="8" t="s">
-        <v>22</v>
       </c>
       <c r="G3" s="4"/>
       <c r="H3" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="I3" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="I3" s="4" t="s">
-        <v>16</v>
-      </c>
       <c r="J3" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K3" s="4"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="C4" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="E4" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="C4" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="E4" s="8" t="s">
+      <c r="F4" s="8" t="s">
         <v>26</v>
-      </c>
-      <c r="F4" s="8" t="s">
-        <v>27</v>
       </c>
       <c r="G4" s="4"/>
       <c r="H4" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="I4" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="I4" s="4" t="s">
-        <v>16</v>
-      </c>
       <c r="J4" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="K4" s="4"/>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="C5" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="E5" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="C5" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="E5" s="8" t="s">
+      <c r="F5" s="8" t="s">
         <v>31</v>
-      </c>
-      <c r="F5" s="8" t="s">
-        <v>32</v>
       </c>
       <c r="G5" s="4"/>
       <c r="H5" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="I5" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="I5" s="4" t="s">
+      <c r="J5" s="4" t="s">
         <v>34</v>
-      </c>
-      <c r="J5" s="4" t="s">
-        <v>35</v>
       </c>
       <c r="K5" s="4"/>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B6" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="C6" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="E6" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="C6" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="E6" s="8" t="s">
+      <c r="F6" s="8" t="s">
         <v>38</v>
-      </c>
-      <c r="F6" s="8" t="s">
-        <v>39</v>
       </c>
       <c r="G6" s="4"/>
       <c r="H6" s="8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I6" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="J6" s="4" t="s">
         <v>40</v>
-      </c>
-      <c r="J6" s="4" t="s">
-        <v>41</v>
       </c>
       <c r="K6" s="4"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B7" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="C7" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="E7" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="C7" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="E7" s="8" t="s">
+      <c r="F7" s="8" t="s">
         <v>44</v>
-      </c>
-      <c r="F7" s="8" t="s">
-        <v>45</v>
       </c>
       <c r="G7" s="4"/>
       <c r="H7" s="8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I7" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="J7" s="4" t="s">
         <v>46</v>
-      </c>
-      <c r="J7" s="4" t="s">
-        <v>47</v>
       </c>
       <c r="K7" s="4"/>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B8" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="C8" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="E8" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="C8" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="E8" s="8" t="s">
+      <c r="F8" s="8" t="s">
         <v>50</v>
-      </c>
-      <c r="F8" s="8" t="s">
-        <v>51</v>
       </c>
       <c r="G8" s="4"/>
       <c r="H8" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="I8" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="J8" s="4" t="s">
         <v>52</v>
-      </c>
-      <c r="I8" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="J8" s="4" t="s">
-        <v>53</v>
       </c>
       <c r="K8" s="4"/>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B9" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="C9" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="E9" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="C9" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="E9" s="8" t="s">
+      <c r="F9" s="8" t="s">
         <v>56</v>
-      </c>
-      <c r="F9" s="8" t="s">
-        <v>57</v>
       </c>
       <c r="G9" s="4"/>
       <c r="H9" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I9" s="4"/>
       <c r="J9" s="4"/>
@@ -1131,47 +1132,47 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="B10" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="C10" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="E10" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="C10" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="E10" s="8" t="s">
+      <c r="F10" s="8" t="s">
         <v>61</v>
-      </c>
-      <c r="F10" s="8" t="s">
-        <v>62</v>
       </c>
       <c r="G10" s="4"/>
       <c r="H10" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="I10" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="I10" s="4" t="s">
-        <v>16</v>
-      </c>
       <c r="J10" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="K10" s="4"/>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E11" s="8">
         <v>37.483620999999999</v>
@@ -1184,23 +1185,23 @@
         <v>7000</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J11" s="4"/>
       <c r="K11" s="4"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E12" s="8">
         <v>37.487240999999997</v>
@@ -1213,25 +1214,25 @@
         <v>7500</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J12" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="K12" s="4"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E13" s="8">
         <v>37.486063999999999</v>
@@ -1244,25 +1245,25 @@
         <v>8200</v>
       </c>
       <c r="I13" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="J13" s="4" t="s">
         <v>83</v>
-      </c>
-      <c r="J13" s="4" t="s">
-        <v>84</v>
       </c>
       <c r="K13" s="4"/>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B14" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="D14" s="3" t="s">
         <v>85</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>86</v>
       </c>
       <c r="E14" s="9">
         <v>37.485253999999998</v>
@@ -1275,56 +1276,56 @@
         <v>8000</v>
       </c>
       <c r="I14" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="J14" s="3" t="s">
         <v>87</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>88</v>
       </c>
       <c r="K14" s="3"/>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B15" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="E15" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="C15" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="E15" s="9" t="s">
+      <c r="F15" s="9" t="s">
         <v>66</v>
-      </c>
-      <c r="F15" s="9" t="s">
-        <v>67</v>
       </c>
       <c r="G15" s="3"/>
       <c r="H15" s="9">
         <v>8000</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K15" s="3"/>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" s="11" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E16" s="13">
         <v>37.414121700000003</v>
@@ -1337,25 +1338,25 @@
         <v>9000</v>
       </c>
       <c r="I16" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="J16" s="14" t="s">
         <v>108</v>
-      </c>
-      <c r="J16" s="14" t="s">
-        <v>109</v>
       </c>
       <c r="K16" s="15"/>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" s="11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E17" s="13">
         <v>37.416232999999998</v>
@@ -1368,27 +1369,27 @@
         <v>8000</v>
       </c>
       <c r="I17" s="11" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="J17" s="11" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="K17" s="11" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" s="11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B18" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="C18" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="D18" s="11" t="s">
         <v>116</v>
-      </c>
-      <c r="C18" s="11" t="s">
-        <v>105</v>
-      </c>
-      <c r="D18" s="11" t="s">
-        <v>117</v>
       </c>
       <c r="E18" s="13">
         <v>37.417220399999998</v>
@@ -1401,16 +1402,16 @@
         <v>8500</v>
       </c>
       <c r="I18" s="11" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="J18" s="11"/>
       <c r="K18" s="11" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B19" s="7"/>
       <c r="C19" s="3"/>
@@ -1425,13 +1426,13 @@
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B20" s="7"/>
       <c r="C20" s="3"/>
       <c r="D20" s="3"/>
       <c r="E20" s="9" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F20" s="9"/>
       <c r="G20" s="3"/>
@@ -1442,7 +1443,7 @@
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B21" s="7"/>
       <c r="C21" s="3"/>

--- a/data/restaurants.xlsx
+++ b/data/restaurants.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\woody\Documents\AI_개발\my-restaurant-map\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{719EEB8D-1301-4CB2-854B-4315B6F2409D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90363706-0C30-4693-A21D-D820C1FE435F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="270" yWindow="720" windowWidth="18975" windowHeight="15285" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="179">
   <si>
     <t>id</t>
   </si>
@@ -2611,7 +2611,9 @@
     <row r="52" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A52" s="1"/>
       <c r="B52" s="4"/>
-      <c r="C52" s="1"/>
+      <c r="C52" s="8" t="s">
+        <v>76</v>
+      </c>
       <c r="D52" s="17"/>
       <c r="E52" s="6"/>
       <c r="F52" s="6"/>

--- a/data/restaurants.xlsx
+++ b/data/restaurants.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\woody\Documents\AI_개발\my-restaurant-map\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\woody\Documents\AI_개발\Marble-Table\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90363706-0C30-4693-A21D-D820C1FE435F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FFFEF06-EBD7-4044-A2A9-7F71FD8CB880}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="270" yWindow="720" windowWidth="18975" windowHeight="15285" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="270" yWindow="720" windowWidth="25980" windowHeight="15285" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="restaurants" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="192">
   <si>
     <t>id</t>
   </si>
@@ -783,6 +783,58 @@
   </si>
   <si>
     <t>https://www.instagram.com/sodam_mullae/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>어메이징키친 한식뷔페</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>서울특별시 영등포구 국회대로54길 10 아크로타워 스퀘어 상가 13동 B29</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://pf.kakao.com/_qKKAG</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>중식 11:00~14:30</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>밥플러스 슈퍼스타 당산생각공장</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>서울특별시 영등포구 영등포로 150 1층</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>중식 11:00~14:00, 석식 17:30~19:20</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://pf.kakao.com/_xmbxnGG</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>다올푸드 구내식당</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>서울특별시 영등포구 양산로 57-5 1층 106,107호(양평동 이노플렉스)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>오늘의밥상</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>서울특별시 영등포구 선유로9길 10 문래 sk v1 center 1층</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.instagram.com/jins_onlbabsang</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -910,7 +962,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -945,6 +997,7 @@
     <xf numFmtId="3" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -1247,7 +1300,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K59"/>
+  <dimension ref="A1:K61"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="26.25" bestFit="1" customWidth="1"/>
@@ -2469,266 +2522,326 @@
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A45" s="1"/>
-      <c r="B45" s="4"/>
-      <c r="C45" s="1"/>
-      <c r="D45" s="1"/>
-      <c r="E45" s="6"/>
-      <c r="F45" s="6"/>
+      <c r="B45" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="E45" s="6">
+        <v>37.522919899999998</v>
+      </c>
+      <c r="F45" s="6">
+        <v>126.9061335</v>
+      </c>
       <c r="G45" s="1"/>
-      <c r="H45" s="11"/>
-      <c r="I45" s="1"/>
+      <c r="H45" s="11">
+        <v>8500</v>
+      </c>
+      <c r="I45" s="1" t="s">
+        <v>182</v>
+      </c>
       <c r="J45" s="1"/>
-      <c r="K45" s="1"/>
+      <c r="K45" s="20" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A46" s="1"/>
-      <c r="B46" s="4"/>
-      <c r="C46" s="1"/>
-      <c r="D46" s="1"/>
-      <c r="E46" s="6"/>
-      <c r="F46" s="6"/>
+      <c r="B46" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="E46" s="6">
+        <v>37.520604900000002</v>
+      </c>
+      <c r="F46" s="6">
+        <v>126.8975058</v>
+      </c>
       <c r="G46" s="1"/>
-      <c r="H46" s="19"/>
-      <c r="I46" s="1"/>
+      <c r="H46" s="19">
+        <v>9000</v>
+      </c>
+      <c r="I46" s="1" t="s">
+        <v>185</v>
+      </c>
       <c r="J46" s="1"/>
-      <c r="K46" s="1"/>
+      <c r="K46" s="20" t="s">
+        <v>186</v>
+      </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A47" s="1"/>
-      <c r="B47" s="4"/>
-      <c r="C47" s="1"/>
-      <c r="D47" s="1"/>
-      <c r="E47" s="6"/>
-      <c r="F47" s="6"/>
+      <c r="B47" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="E47" s="6">
+        <v>37.525516699999997</v>
+      </c>
+      <c r="F47" s="6">
+        <v>126.8893619</v>
+      </c>
       <c r="G47" s="1"/>
-      <c r="H47" s="6"/>
-      <c r="I47" s="1"/>
+      <c r="H47" s="19"/>
+      <c r="I47" s="1" t="s">
+        <v>95</v>
+      </c>
       <c r="J47" s="1"/>
-      <c r="K47" s="1"/>
+      <c r="K47" s="20"/>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A48" s="1"/>
-      <c r="B48" s="1"/>
-      <c r="C48" s="1"/>
-      <c r="D48" s="1"/>
-      <c r="E48" s="1"/>
-      <c r="F48" s="1"/>
+      <c r="B48" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="E48" s="6">
+        <v>37.517841099999998</v>
+      </c>
+      <c r="F48" s="6">
+        <v>126.88722660000001</v>
+      </c>
       <c r="G48" s="1"/>
-      <c r="H48" s="1"/>
-      <c r="I48" s="1"/>
-      <c r="J48" s="1"/>
-      <c r="K48" s="1"/>
+      <c r="H48" s="11">
+        <v>6600</v>
+      </c>
+      <c r="I48" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="J48" s="20" t="s">
+        <v>191</v>
+      </c>
+      <c r="K48" s="20"/>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A49" s="8"/>
-      <c r="B49" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="C49" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="D49" s="16" t="s">
-        <v>81</v>
-      </c>
-      <c r="E49" s="9">
-        <v>37.414121700000003</v>
-      </c>
-      <c r="F49" s="9">
-        <v>126.978489</v>
-      </c>
-      <c r="G49" s="8"/>
-      <c r="H49" s="12">
-        <v>9000</v>
-      </c>
-      <c r="I49" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="J49" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="K49" s="8"/>
+      <c r="A49" s="1"/>
+      <c r="B49" s="4"/>
+      <c r="C49" s="1"/>
+      <c r="D49" s="1"/>
+      <c r="E49" s="6"/>
+      <c r="F49" s="6"/>
+      <c r="G49" s="1"/>
+      <c r="H49" s="6"/>
+      <c r="I49" s="1"/>
+      <c r="J49" s="1"/>
+      <c r="K49" s="1"/>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A50" s="8"/>
-      <c r="B50" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="C50" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="D50" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="E50" s="9">
-        <v>37.416232999999998</v>
-      </c>
-      <c r="F50" s="9">
-        <v>126.97617579999999</v>
-      </c>
-      <c r="G50" s="8"/>
-      <c r="H50" s="12">
-        <v>8000</v>
-      </c>
-      <c r="I50" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="J50" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="K50" s="8" t="s">
-        <v>85</v>
-      </c>
+      <c r="A50" s="1"/>
+      <c r="B50" s="1"/>
+      <c r="C50" s="1"/>
+      <c r="D50" s="1"/>
+      <c r="E50" s="1"/>
+      <c r="F50" s="1"/>
+      <c r="G50" s="1"/>
+      <c r="H50" s="1"/>
+      <c r="I50" s="1"/>
+      <c r="J50" s="1"/>
+      <c r="K50" s="1"/>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A51" s="8"/>
       <c r="B51" s="7" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="C51" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="D51" s="8" t="s">
-        <v>87</v>
+      <c r="D51" s="16" t="s">
+        <v>81</v>
       </c>
       <c r="E51" s="9">
-        <v>37.417220399999998</v>
+        <v>37.414121700000003</v>
       </c>
       <c r="F51" s="9">
-        <v>126.97502830000001</v>
+        <v>126.978489</v>
       </c>
       <c r="G51" s="8"/>
       <c r="H51" s="12">
-        <v>8500</v>
+        <v>9000</v>
       </c>
       <c r="I51" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="J51" s="8"/>
-      <c r="K51" s="8" t="s">
-        <v>88</v>
-      </c>
+        <v>78</v>
+      </c>
+      <c r="J51" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="K51" s="8"/>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A52" s="1"/>
-      <c r="B52" s="4"/>
+      <c r="A52" s="8"/>
+      <c r="B52" s="7" t="s">
+        <v>84</v>
+      </c>
       <c r="C52" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="D52" s="17"/>
-      <c r="E52" s="6"/>
-      <c r="F52" s="6"/>
-      <c r="G52" s="1"/>
-      <c r="H52" s="6"/>
-      <c r="I52" s="1"/>
-      <c r="J52" s="1"/>
-      <c r="K52" s="1"/>
+      <c r="D52" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="E52" s="9">
+        <v>37.416232999999998</v>
+      </c>
+      <c r="F52" s="9">
+        <v>126.97617579999999</v>
+      </c>
+      <c r="G52" s="8"/>
+      <c r="H52" s="12">
+        <v>8000</v>
+      </c>
+      <c r="I52" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="J52" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="K52" s="8" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A53" s="1"/>
-      <c r="B53" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="C53" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="D53" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="E53" s="6">
-        <v>37.461079300000002</v>
-      </c>
-      <c r="F53" s="6">
-        <v>126.87630040000001</v>
-      </c>
-      <c r="G53" s="1"/>
-      <c r="H53" s="11">
-        <v>7000</v>
-      </c>
-      <c r="I53" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="J53" s="1"/>
-      <c r="K53" s="1"/>
+      <c r="A53" s="8"/>
+      <c r="B53" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="C53" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="D53" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="E53" s="9">
+        <v>37.417220399999998</v>
+      </c>
+      <c r="F53" s="9">
+        <v>126.97502830000001</v>
+      </c>
+      <c r="G53" s="8"/>
+      <c r="H53" s="12">
+        <v>8500</v>
+      </c>
+      <c r="I53" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="J53" s="8"/>
+      <c r="K53" s="8" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A54" s="1"/>
-      <c r="B54" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="C54" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="D54" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="E54" s="6">
-        <v>37.4477519</v>
-      </c>
-      <c r="F54" s="6">
-        <v>126.89218219999999</v>
-      </c>
+      <c r="B54" s="4"/>
+      <c r="C54" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="D54" s="17"/>
+      <c r="E54" s="6"/>
+      <c r="F54" s="6"/>
       <c r="G54" s="1"/>
       <c r="H54" s="6"/>
-      <c r="I54" s="1" t="s">
-        <v>107</v>
-      </c>
+      <c r="I54" s="1"/>
       <c r="J54" s="1"/>
       <c r="K54" s="1"/>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A55" s="1"/>
       <c r="B55" s="4" t="s">
-        <v>166</v>
+        <v>154</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>153</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="E55" s="6">
-        <v>37.445887599999999</v>
+        <v>37.461079300000002</v>
       </c>
       <c r="F55" s="6">
-        <v>126.89412780000001</v>
+        <v>126.87630040000001</v>
       </c>
       <c r="G55" s="1"/>
-      <c r="H55" s="6">
-        <v>8000</v>
+      <c r="H55" s="11">
+        <v>7000</v>
       </c>
       <c r="I55" s="1" t="s">
-        <v>95</v>
+        <v>156</v>
       </c>
       <c r="J55" s="1"/>
-      <c r="K55" s="1" t="s">
-        <v>168</v>
-      </c>
+      <c r="K55" s="1"/>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A56" s="1"/>
-      <c r="B56" s="4"/>
-      <c r="C56" s="1"/>
-      <c r="D56" s="1"/>
-      <c r="E56" s="6"/>
-      <c r="F56" s="6"/>
+      <c r="B56" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="E56" s="6">
+        <v>37.4477519</v>
+      </c>
+      <c r="F56" s="6">
+        <v>126.89218219999999</v>
+      </c>
       <c r="G56" s="1"/>
       <c r="H56" s="6"/>
-      <c r="I56" s="1"/>
+      <c r="I56" s="1" t="s">
+        <v>107</v>
+      </c>
       <c r="J56" s="1"/>
       <c r="K56" s="1"/>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A57" s="1"/>
-      <c r="B57" s="4"/>
-      <c r="C57" s="1"/>
-      <c r="D57" s="1"/>
-      <c r="E57" s="6"/>
-      <c r="F57" s="6"/>
+      <c r="B57" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="E57" s="6">
+        <v>37.445887599999999</v>
+      </c>
+      <c r="F57" s="6">
+        <v>126.89412780000001</v>
+      </c>
       <c r="G57" s="1"/>
-      <c r="H57" s="6"/>
-      <c r="I57" s="1"/>
+      <c r="H57" s="6">
+        <v>8000</v>
+      </c>
+      <c r="I57" s="1" t="s">
+        <v>95</v>
+      </c>
       <c r="J57" s="1"/>
-      <c r="K57" s="1"/>
+      <c r="K57" s="1" t="s">
+        <v>168</v>
+      </c>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A58" s="1"/>
@@ -2756,6 +2869,32 @@
       <c r="J59" s="1"/>
       <c r="K59" s="1"/>
     </row>
+    <row r="60" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A60" s="1"/>
+      <c r="B60" s="4"/>
+      <c r="C60" s="1"/>
+      <c r="D60" s="1"/>
+      <c r="E60" s="6"/>
+      <c r="F60" s="6"/>
+      <c r="G60" s="1"/>
+      <c r="H60" s="6"/>
+      <c r="I60" s="1"/>
+      <c r="J60" s="1"/>
+      <c r="K60" s="1"/>
+    </row>
+    <row r="61" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A61" s="1"/>
+      <c r="B61" s="4"/>
+      <c r="C61" s="1"/>
+      <c r="D61" s="1"/>
+      <c r="E61" s="6"/>
+      <c r="F61" s="6"/>
+      <c r="G61" s="1"/>
+      <c r="H61" s="6"/>
+      <c r="I61" s="1"/>
+      <c r="J61" s="1"/>
+      <c r="K61" s="1"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/restaurants.xlsx
+++ b/data/restaurants.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\woody\Documents\AI_개발\Marble-Table\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FFFEF06-EBD7-4044-A2A9-7F71FD8CB880}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D382BCD-8001-40E8-8DFC-2622DF39C6CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="270" yWindow="720" windowWidth="25980" windowHeight="15285" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="35145" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="restaurants" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="195">
   <si>
     <t>id</t>
   </si>
@@ -835,6 +835,18 @@
   </si>
   <si>
     <t>https://www.instagram.com/jins_onlbabsang</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>티시스 영등포</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>서울특별시 영등포구 버드나루로2길 7 흥국생명빌딩 지하 1층</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>중식 11:30~14:00</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -962,7 +974,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -997,7 +1009,6 @@
     <xf numFmtId="3" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -2545,7 +2556,7 @@
         <v>182</v>
       </c>
       <c r="J45" s="1"/>
-      <c r="K45" s="20" t="s">
+      <c r="K45" t="s">
         <v>181</v>
       </c>
     </row>
@@ -2574,7 +2585,7 @@
         <v>185</v>
       </c>
       <c r="J46" s="1"/>
-      <c r="K46" s="20" t="s">
+      <c r="K46" t="s">
         <v>186</v>
       </c>
     </row>
@@ -2601,7 +2612,6 @@
         <v>95</v>
       </c>
       <c r="J47" s="1"/>
-      <c r="K47" s="20"/>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A48" s="1"/>
@@ -2627,21 +2637,34 @@
       <c r="I48" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="J48" s="20" t="s">
+      <c r="J48" t="s">
         <v>191</v>
       </c>
-      <c r="K48" s="20"/>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A49" s="1"/>
-      <c r="B49" s="4"/>
-      <c r="C49" s="1"/>
-      <c r="D49" s="1"/>
-      <c r="E49" s="6"/>
-      <c r="F49" s="6"/>
+      <c r="B49" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="E49" s="6">
+        <v>37.5209689</v>
+      </c>
+      <c r="F49" s="6">
+        <v>126.91331839999999</v>
+      </c>
       <c r="G49" s="1"/>
-      <c r="H49" s="6"/>
-      <c r="I49" s="1"/>
+      <c r="H49" s="11">
+        <v>6500</v>
+      </c>
+      <c r="I49" s="1" t="s">
+        <v>194</v>
+      </c>
       <c r="J49" s="1"/>
       <c r="K49" s="1"/>
     </row>
@@ -2750,9 +2773,7 @@
     <row r="54" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A54" s="1"/>
       <c r="B54" s="4"/>
-      <c r="C54" s="8" t="s">
-        <v>76</v>
-      </c>
+      <c r="C54" s="18"/>
       <c r="D54" s="17"/>
       <c r="E54" s="6"/>
       <c r="F54" s="6"/>
@@ -2898,5 +2919,6 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/data/restaurants.xlsx
+++ b/data/restaurants.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\woody\Documents\AI_개발\Marble-Table\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D382BCD-8001-40E8-8DFC-2622DF39C6CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75764908-EE28-4FDD-A974-90EC7751E161}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="35145" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="450" yWindow="45" windowWidth="31530" windowHeight="15210" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="restaurants" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="199">
   <si>
     <t>id</t>
   </si>
@@ -847,6 +847,22 @@
   </si>
   <si>
     <t>중식 11:30~14:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>밥플렉스</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>서울특별시 구로구 디지털로 243 제비1층 제114, 115호</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>중식 11:00~13:40</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.instagram.com/babflex_guro/</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -974,7 +990,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1009,6 +1025,7 @@
     <xf numFmtId="3" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -1311,7 +1328,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K61"/>
+  <dimension ref="A1:K62"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="26.25" bestFit="1" customWidth="1"/>
@@ -1705,136 +1722,138 @@
       <c r="K13" s="2"/>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A14" s="1"/>
-      <c r="B14" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="E14" s="6">
-        <v>37.485253999999998</v>
-      </c>
-      <c r="F14" s="6">
-        <v>126.87745099999999</v>
-      </c>
-      <c r="G14" s="1"/>
-      <c r="H14" s="11">
-        <v>8000</v>
-      </c>
-      <c r="I14" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="J14" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="K14" s="1"/>
+      <c r="A14" s="2"/>
+      <c r="B14" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="E14" s="5">
+        <v>37.481776099999998</v>
+      </c>
+      <c r="F14" s="5">
+        <v>126.8923293</v>
+      </c>
+      <c r="G14" s="2"/>
+      <c r="H14" s="10">
+        <v>8500</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="J14" s="20" t="s">
+        <v>198</v>
+      </c>
+      <c r="K14" s="2"/>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" s="1"/>
       <c r="B15" s="4" t="s">
-        <v>90</v>
+        <v>58</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="D15" s="18" t="s">
-        <v>92</v>
+      <c r="D15" s="1" t="s">
+        <v>59</v>
       </c>
       <c r="E15" s="6">
-        <v>37.4796336</v>
+        <v>37.485253999999998</v>
       </c>
       <c r="F15" s="6">
-        <v>126.8873856</v>
+        <v>126.87745099999999</v>
       </c>
       <c r="G15" s="1"/>
-      <c r="H15" s="19">
-        <v>7000</v>
-      </c>
-      <c r="I15" s="18" t="s">
-        <v>97</v>
-      </c>
-      <c r="J15" s="1"/>
+      <c r="H15" s="11">
+        <v>8000</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="J15" s="1" t="s">
+        <v>60</v>
+      </c>
       <c r="K15" s="1"/>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" s="1"/>
       <c r="B16" s="4" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="D16" s="1" t="s">
-        <v>99</v>
+      <c r="D16" s="18" t="s">
+        <v>92</v>
       </c>
       <c r="E16" s="6">
-        <v>37.480060899999998</v>
+        <v>37.4796336</v>
       </c>
       <c r="F16" s="6">
-        <v>126.8870524</v>
+        <v>126.8873856</v>
       </c>
       <c r="G16" s="1"/>
       <c r="H16" s="19">
-        <v>7500</v>
-      </c>
-      <c r="I16" s="18"/>
+        <v>7000</v>
+      </c>
+      <c r="I16" s="18" t="s">
+        <v>97</v>
+      </c>
       <c r="J16" s="1"/>
       <c r="K16" s="1"/>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" s="1"/>
       <c r="B17" s="4" t="s">
-        <v>114</v>
+        <v>98</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>75</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>115</v>
+        <v>99</v>
       </c>
       <c r="E17" s="6">
-        <v>37.481243499999998</v>
+        <v>37.480060899999998</v>
       </c>
       <c r="F17" s="6">
-        <v>126.886263</v>
+        <v>126.8870524</v>
       </c>
       <c r="G17" s="1"/>
       <c r="H17" s="19">
-        <v>7000</v>
-      </c>
-      <c r="I17" s="18" t="s">
-        <v>95</v>
-      </c>
+        <v>7500</v>
+      </c>
+      <c r="I17" s="18"/>
       <c r="J17" s="1"/>
       <c r="K17" s="1"/>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" s="1"/>
       <c r="B18" s="4" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>75</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="E18" s="6">
-        <v>37.478887700000001</v>
+        <v>37.481243499999998</v>
       </c>
       <c r="F18" s="6">
-        <v>126.8860076</v>
+        <v>126.886263</v>
       </c>
       <c r="G18" s="1"/>
       <c r="H18" s="19">
         <v>7000</v>
       </c>
       <c r="I18" s="18" t="s">
-        <v>107</v>
+        <v>95</v>
       </c>
       <c r="J18" s="1"/>
       <c r="K18" s="1"/>
@@ -1842,165 +1861,165 @@
     <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" s="1"/>
       <c r="B19" s="4" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>75</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="E19" s="6">
-        <v>37.480209600000002</v>
+        <v>37.478887700000001</v>
       </c>
       <c r="F19" s="6">
-        <v>126.88511889999999</v>
+        <v>126.8860076</v>
       </c>
       <c r="G19" s="1"/>
       <c r="H19" s="19">
-        <v>7500</v>
+        <v>7000</v>
       </c>
       <c r="I19" s="18" t="s">
-        <v>95</v>
-      </c>
-      <c r="J19" s="1" t="s">
-        <v>110</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="J19" s="1"/>
       <c r="K19" s="1"/>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" s="1"/>
       <c r="B20" s="4" t="s">
-        <v>49</v>
+        <v>108</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>75</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="E20" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="F20" s="6" t="s">
-        <v>51</v>
+        <v>109</v>
+      </c>
+      <c r="E20" s="6">
+        <v>37.480209600000002</v>
+      </c>
+      <c r="F20" s="6">
+        <v>126.88511889999999</v>
       </c>
       <c r="G20" s="1"/>
       <c r="H20" s="19">
-        <v>8000</v>
+        <v>7500</v>
       </c>
       <c r="I20" s="18" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>52</v>
+        <v>110</v>
       </c>
       <c r="K20" s="1"/>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21" s="1"/>
       <c r="B21" s="4" t="s">
-        <v>111</v>
+        <v>49</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>75</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="E21" s="6">
-        <v>37.479549499999997</v>
-      </c>
-      <c r="F21" s="6">
-        <v>126.88453130000001</v>
+        <v>91</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="F21" s="6" t="s">
+        <v>51</v>
       </c>
       <c r="G21" s="1"/>
       <c r="H21" s="19">
-        <v>7500</v>
+        <v>8000</v>
       </c>
       <c r="I21" s="18" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>113</v>
+        <v>52</v>
       </c>
       <c r="K21" s="1"/>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" s="1"/>
       <c r="B22" s="4" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>75</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="E22" s="6">
-        <v>37.4767188</v>
+        <v>37.479549499999997</v>
       </c>
       <c r="F22" s="6">
-        <v>126.8858609</v>
+        <v>126.88453130000001</v>
       </c>
       <c r="G22" s="1"/>
       <c r="H22" s="19">
         <v>7500</v>
       </c>
-      <c r="I22" s="18"/>
-      <c r="J22" s="1"/>
+      <c r="I22" s="18" t="s">
+        <v>107</v>
+      </c>
+      <c r="J22" s="1" t="s">
+        <v>113</v>
+      </c>
       <c r="K22" s="1"/>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23" s="1"/>
       <c r="B23" s="4" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>75</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="E23" s="6">
-        <v>37.475984599999997</v>
+        <v>37.4767188</v>
       </c>
       <c r="F23" s="6">
-        <v>126.88616380000001</v>
+        <v>126.8858609</v>
       </c>
       <c r="G23" s="1"/>
       <c r="H23" s="19">
         <v>7500</v>
       </c>
-      <c r="I23" s="18" t="s">
-        <v>102</v>
-      </c>
+      <c r="I23" s="18"/>
       <c r="J23" s="1"/>
       <c r="K23" s="1"/>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24" s="1"/>
       <c r="B24" s="4" t="s">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>75</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>126</v>
+        <v>101</v>
       </c>
       <c r="E24" s="6">
-        <v>37.476084899999996</v>
+        <v>37.475984599999997</v>
       </c>
       <c r="F24" s="6">
-        <v>126.8800928</v>
+        <v>126.88616380000001</v>
       </c>
       <c r="G24" s="1"/>
       <c r="H24" s="19">
-        <v>7000</v>
+        <v>7500</v>
       </c>
       <c r="I24" s="18" t="s">
-        <v>127</v>
+        <v>102</v>
       </c>
       <c r="J24" s="1"/>
       <c r="K24" s="1"/>
@@ -2008,71 +2027,71 @@
     <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25" s="1"/>
       <c r="B25" s="4" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>75</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="E25" s="6">
-        <v>37.4858209</v>
+        <v>37.476084899999996</v>
       </c>
       <c r="F25" s="6">
-        <v>126.8783535</v>
+        <v>126.8800928</v>
       </c>
       <c r="G25" s="1"/>
       <c r="H25" s="19">
-        <v>6500</v>
-      </c>
-      <c r="I25" s="18"/>
+        <v>7000</v>
+      </c>
+      <c r="I25" s="18" t="s">
+        <v>127</v>
+      </c>
       <c r="J25" s="1"/>
       <c r="K25" s="1"/>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26" s="1"/>
       <c r="B26" s="4" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>75</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="E26" s="6">
-        <v>37.480069800000003</v>
+        <v>37.4858209</v>
       </c>
       <c r="F26" s="6">
-        <v>126.8826835</v>
+        <v>126.8783535</v>
       </c>
       <c r="G26" s="1"/>
       <c r="H26" s="19">
-        <v>8000</v>
-      </c>
-      <c r="I26" s="18" t="s">
-        <v>95</v>
-      </c>
+        <v>6500</v>
+      </c>
+      <c r="I26" s="18"/>
       <c r="J26" s="1"/>
       <c r="K26" s="1"/>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27" s="1"/>
       <c r="B27" s="4" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>75</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="E27" s="6">
-        <v>37.478180100000003</v>
+        <v>37.480069800000003</v>
       </c>
       <c r="F27" s="6">
-        <v>126.8816056</v>
+        <v>126.8826835</v>
       </c>
       <c r="G27" s="1"/>
       <c r="H27" s="19">
@@ -2087,750 +2106,752 @@
     <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28" s="1"/>
       <c r="B28" s="4" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>75</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="E28" s="6">
-        <v>37.480840100000002</v>
+        <v>37.478180100000003</v>
       </c>
       <c r="F28" s="6">
-        <v>126.8777006</v>
+        <v>126.8816056</v>
       </c>
       <c r="G28" s="1"/>
       <c r="H28" s="19">
-        <v>7500</v>
+        <v>8000</v>
       </c>
       <c r="I28" s="18" t="s">
         <v>95</v>
       </c>
       <c r="J28" s="1"/>
-      <c r="K28" s="1" t="s">
-        <v>120</v>
-      </c>
+      <c r="K28" s="1"/>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A29" s="1"/>
       <c r="B29" s="4" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>75</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="E29" s="6">
-        <v>37.474955000000001</v>
+        <v>37.480840100000002</v>
       </c>
       <c r="F29" s="6">
-        <v>126.8818011</v>
+        <v>126.8777006</v>
       </c>
       <c r="G29" s="1"/>
       <c r="H29" s="19">
-        <v>6500</v>
+        <v>7500</v>
       </c>
       <c r="I29" s="18" t="s">
-        <v>107</v>
+        <v>95</v>
       </c>
       <c r="J29" s="1"/>
-      <c r="K29" s="1"/>
+      <c r="K29" s="1" t="s">
+        <v>120</v>
+      </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A30" s="1"/>
       <c r="B30" s="4" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>75</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E30" s="6">
-        <v>37.472730499999997</v>
+        <v>37.474955000000001</v>
       </c>
       <c r="F30" s="6">
-        <v>126.8827223</v>
+        <v>126.8818011</v>
       </c>
       <c r="G30" s="1"/>
       <c r="H30" s="19">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="I30" s="18" t="s">
-        <v>133</v>
-      </c>
-      <c r="J30" s="1" t="s">
-        <v>132</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="J30" s="1"/>
       <c r="K30" s="1"/>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A31" s="1"/>
       <c r="B31" s="4" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>75</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="E31" s="6">
-        <v>37.472303099999998</v>
+        <v>37.472730499999997</v>
       </c>
       <c r="F31" s="6">
-        <v>126.8832507</v>
+        <v>126.8827223</v>
       </c>
       <c r="G31" s="1"/>
       <c r="H31" s="19">
         <v>7500</v>
       </c>
-      <c r="I31" s="18"/>
-      <c r="J31" s="1"/>
+      <c r="I31" s="18" t="s">
+        <v>133</v>
+      </c>
+      <c r="J31" s="1" t="s">
+        <v>132</v>
+      </c>
       <c r="K31" s="1"/>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A32" s="1"/>
       <c r="B32" s="4" t="s">
-        <v>86</v>
+        <v>134</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>75</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E32" s="6">
-        <v>37.470914399999998</v>
+        <v>37.472303099999998</v>
       </c>
       <c r="F32" s="6">
-        <v>126.8837085</v>
+        <v>126.8832507</v>
       </c>
       <c r="G32" s="1"/>
       <c r="H32" s="19">
         <v>7500</v>
       </c>
-      <c r="I32" s="18" t="s">
-        <v>133</v>
-      </c>
-      <c r="J32" s="1" t="s">
-        <v>137</v>
-      </c>
+      <c r="I32" s="18"/>
+      <c r="J32" s="1"/>
       <c r="K32" s="1"/>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A33" s="1"/>
       <c r="B33" s="4" t="s">
-        <v>138</v>
+        <v>86</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>75</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="E33" s="6">
-        <v>37.469678100000003</v>
+        <v>37.470914399999998</v>
       </c>
       <c r="F33" s="6">
-        <v>126.8842518</v>
+        <v>126.8837085</v>
       </c>
       <c r="G33" s="1"/>
-      <c r="H33" s="19"/>
+      <c r="H33" s="19">
+        <v>7500</v>
+      </c>
       <c r="I33" s="18" t="s">
-        <v>140</v>
-      </c>
-      <c r="J33" s="1"/>
+        <v>133</v>
+      </c>
+      <c r="J33" s="1" t="s">
+        <v>137</v>
+      </c>
       <c r="K33" s="1"/>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A34" s="1"/>
       <c r="B34" s="4" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>75</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="E34" s="6">
-        <v>37.471340400000003</v>
+        <v>37.469678100000003</v>
       </c>
       <c r="F34" s="6">
-        <v>126.88632440000001</v>
+        <v>126.8842518</v>
       </c>
       <c r="G34" s="1"/>
-      <c r="H34" s="19">
-        <v>8000</v>
-      </c>
+      <c r="H34" s="19"/>
       <c r="I34" s="18" t="s">
-        <v>95</v>
-      </c>
-      <c r="J34" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="K34" s="1" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="35" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
+        <v>140</v>
+      </c>
+      <c r="J34" s="1"/>
+      <c r="K34" s="1"/>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A35" s="1"/>
       <c r="B35" s="4" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="D35" s="15" t="s">
-        <v>146</v>
+      <c r="D35" s="1" t="s">
+        <v>142</v>
       </c>
       <c r="E35" s="6">
-        <v>37.467635799999996</v>
+        <v>37.471340400000003</v>
       </c>
       <c r="F35" s="6">
-        <v>126.8865041</v>
+        <v>126.88632440000001</v>
       </c>
       <c r="G35" s="1"/>
-      <c r="H35" s="19"/>
-      <c r="I35" s="18"/>
-      <c r="J35" s="1"/>
-      <c r="K35" s="1"/>
-    </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="H35" s="19">
+        <v>8000</v>
+      </c>
+      <c r="I35" s="18" t="s">
+        <v>95</v>
+      </c>
+      <c r="J35" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="K35" s="1" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A36" s="1"/>
       <c r="B36" s="4" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="D36" s="1" t="s">
-        <v>148</v>
+      <c r="D36" s="15" t="s">
+        <v>146</v>
       </c>
       <c r="E36" s="6">
-        <v>37.466851499999997</v>
+        <v>37.467635799999996</v>
       </c>
       <c r="F36" s="6">
-        <v>126.8868415</v>
+        <v>126.8865041</v>
       </c>
       <c r="G36" s="1"/>
-      <c r="H36" s="19">
-        <v>7500</v>
-      </c>
-      <c r="I36" s="18" t="s">
-        <v>95</v>
-      </c>
+      <c r="H36" s="19"/>
+      <c r="I36" s="18"/>
       <c r="J36" s="1"/>
       <c r="K36" s="1"/>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A37" s="1"/>
       <c r="B37" s="4" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>75</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="E37" s="6">
-        <v>37.466935200000002</v>
+        <v>37.466851499999997</v>
       </c>
       <c r="F37" s="6">
-        <v>126.8884393</v>
+        <v>126.8868415</v>
       </c>
       <c r="G37" s="1"/>
       <c r="H37" s="19">
-        <v>7800</v>
+        <v>7500</v>
       </c>
       <c r="I37" s="18" t="s">
-        <v>152</v>
-      </c>
-      <c r="J37" s="1" t="s">
-        <v>151</v>
-      </c>
+        <v>95</v>
+      </c>
+      <c r="J37" s="1"/>
       <c r="K37" s="1"/>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A38" s="1"/>
       <c r="B38" s="4" t="s">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>75</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="E38" s="6">
-        <v>37.461021799999997</v>
+        <v>37.466935200000002</v>
       </c>
       <c r="F38" s="6">
-        <v>126.8973929</v>
+        <v>126.8884393</v>
       </c>
       <c r="G38" s="1"/>
       <c r="H38" s="19">
-        <v>7000</v>
+        <v>7800</v>
       </c>
       <c r="I38" s="18" t="s">
-        <v>161</v>
-      </c>
-      <c r="J38" s="1"/>
+        <v>152</v>
+      </c>
+      <c r="J38" s="1" t="s">
+        <v>151</v>
+      </c>
       <c r="K38" s="1"/>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A39" s="1"/>
       <c r="B39" s="4" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>75</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="E39" s="6">
-        <v>37.458534200000003</v>
+        <v>37.461021799999997</v>
       </c>
       <c r="F39" s="6">
-        <v>126.8980512</v>
+        <v>126.8973929</v>
       </c>
       <c r="G39" s="1"/>
-      <c r="H39" s="19"/>
-      <c r="I39" s="18"/>
+      <c r="H39" s="19">
+        <v>7000</v>
+      </c>
+      <c r="I39" s="18" t="s">
+        <v>161</v>
+      </c>
       <c r="J39" s="1"/>
       <c r="K39" s="1"/>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A40" s="1"/>
       <c r="B40" s="4" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>75</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="E40" s="6">
-        <v>37.458589600000003</v>
+        <v>37.458534200000003</v>
       </c>
       <c r="F40" s="6">
-        <v>126.89831599999999</v>
+        <v>126.8980512</v>
       </c>
       <c r="G40" s="1"/>
-      <c r="H40" s="11">
-        <v>7000</v>
-      </c>
-      <c r="I40" s="1" t="s">
-        <v>95</v>
-      </c>
+      <c r="H40" s="19"/>
+      <c r="I40" s="18"/>
       <c r="J40" s="1"/>
       <c r="K40" s="1"/>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A41" s="1"/>
-      <c r="B41" s="4"/>
-      <c r="C41" s="1"/>
-      <c r="D41" s="1"/>
-      <c r="E41" s="6"/>
-      <c r="F41" s="6"/>
+      <c r="B41" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="E41" s="6">
+        <v>37.458589600000003</v>
+      </c>
+      <c r="F41" s="6">
+        <v>126.89831599999999</v>
+      </c>
       <c r="G41" s="1"/>
-      <c r="H41" s="11"/>
-      <c r="I41" s="1"/>
+      <c r="H41" s="11">
+        <v>7000</v>
+      </c>
+      <c r="I41" s="1" t="s">
+        <v>95</v>
+      </c>
       <c r="J41" s="1"/>
       <c r="K41" s="1"/>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A42" s="1"/>
-      <c r="B42" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="D42" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="E42" s="6">
-        <v>37.514773499999997</v>
-      </c>
-      <c r="F42" s="6">
-        <v>126.89749689999999</v>
-      </c>
+      <c r="B42" s="4"/>
+      <c r="C42" s="1"/>
+      <c r="D42" s="1"/>
+      <c r="E42" s="6"/>
+      <c r="F42" s="6"/>
       <c r="G42" s="1"/>
-      <c r="H42" s="11">
-        <v>8000</v>
-      </c>
-      <c r="I42" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="J42" s="1" t="s">
-        <v>172</v>
-      </c>
+      <c r="H42" s="11"/>
+      <c r="I42" s="1"/>
+      <c r="J42" s="1"/>
       <c r="K42" s="1"/>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A43" s="1"/>
       <c r="B43" s="4" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>170</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="E43" s="6" t="s">
-        <v>175</v>
+        <v>171</v>
+      </c>
+      <c r="E43" s="6">
+        <v>37.514773499999997</v>
       </c>
       <c r="F43" s="6">
-        <v>126.8991528</v>
+        <v>126.89749689999999</v>
       </c>
       <c r="G43" s="1"/>
       <c r="H43" s="11">
-        <v>6000</v>
-      </c>
-      <c r="I43" s="1"/>
-      <c r="J43" s="1"/>
+        <v>8000</v>
+      </c>
+      <c r="I43" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="J43" s="1" t="s">
+        <v>172</v>
+      </c>
       <c r="K43" s="1"/>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A44" s="1"/>
       <c r="B44" s="4" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>170</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="E44" s="6">
-        <v>37.516073900000002</v>
+        <v>174</v>
+      </c>
+      <c r="E44" s="6" t="s">
+        <v>175</v>
       </c>
       <c r="F44" s="6">
-        <v>126.88676940000001</v>
+        <v>126.8991528</v>
       </c>
       <c r="G44" s="1"/>
       <c r="H44" s="11">
-        <v>8800</v>
-      </c>
-      <c r="I44" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="J44" s="1" t="s">
-        <v>178</v>
-      </c>
+        <v>6000</v>
+      </c>
+      <c r="I44" s="1"/>
+      <c r="J44" s="1"/>
       <c r="K44" s="1"/>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A45" s="1"/>
       <c r="B45" s="4" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>170</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="E45" s="6">
-        <v>37.522919899999998</v>
+        <v>37.516073900000002</v>
       </c>
       <c r="F45" s="6">
-        <v>126.9061335</v>
+        <v>126.88676940000001</v>
       </c>
       <c r="G45" s="1"/>
       <c r="H45" s="11">
-        <v>8500</v>
+        <v>8800</v>
       </c>
       <c r="I45" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="J45" s="1"/>
-      <c r="K45" t="s">
-        <v>181</v>
-      </c>
+        <v>95</v>
+      </c>
+      <c r="J45" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="K45" s="1"/>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A46" s="1"/>
       <c r="B46" s="4" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>170</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="E46" s="6">
-        <v>37.520604900000002</v>
+        <v>37.522919899999998</v>
       </c>
       <c r="F46" s="6">
-        <v>126.8975058</v>
+        <v>126.9061335</v>
       </c>
       <c r="G46" s="1"/>
-      <c r="H46" s="19">
-        <v>9000</v>
+      <c r="H46" s="11">
+        <v>8500</v>
       </c>
       <c r="I46" s="1" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="J46" s="1"/>
       <c r="K46" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A47" s="1"/>
       <c r="B47" s="4" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>170</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="E47" s="6">
-        <v>37.525516699999997</v>
+        <v>37.520604900000002</v>
       </c>
       <c r="F47" s="6">
-        <v>126.8893619</v>
+        <v>126.8975058</v>
       </c>
       <c r="G47" s="1"/>
-      <c r="H47" s="19"/>
+      <c r="H47" s="19">
+        <v>9000</v>
+      </c>
       <c r="I47" s="1" t="s">
-        <v>95</v>
+        <v>185</v>
       </c>
       <c r="J47" s="1"/>
+      <c r="K47" t="s">
+        <v>186</v>
+      </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A48" s="1"/>
       <c r="B48" s="4" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>170</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E48" s="6">
-        <v>37.517841099999998</v>
+        <v>37.525516699999997</v>
       </c>
       <c r="F48" s="6">
-        <v>126.88722660000001</v>
+        <v>126.8893619</v>
       </c>
       <c r="G48" s="1"/>
-      <c r="H48" s="11">
-        <v>6600</v>
-      </c>
+      <c r="H48" s="19"/>
       <c r="I48" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="J48" t="s">
-        <v>191</v>
-      </c>
+      <c r="J48" s="1"/>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A49" s="1"/>
       <c r="B49" s="4" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>170</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="E49" s="6">
-        <v>37.5209689</v>
+        <v>37.517841099999998</v>
       </c>
       <c r="F49" s="6">
-        <v>126.91331839999999</v>
+        <v>126.88722660000001</v>
       </c>
       <c r="G49" s="1"/>
       <c r="H49" s="11">
-        <v>6500</v>
+        <v>6600</v>
       </c>
       <c r="I49" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="J49" s="1"/>
-      <c r="K49" s="1"/>
+        <v>95</v>
+      </c>
+      <c r="J49" t="s">
+        <v>191</v>
+      </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A50" s="1"/>
-      <c r="B50" s="1"/>
-      <c r="C50" s="1"/>
-      <c r="D50" s="1"/>
-      <c r="E50" s="1"/>
-      <c r="F50" s="1"/>
+      <c r="B50" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="E50" s="6">
+        <v>37.5209689</v>
+      </c>
+      <c r="F50" s="6">
+        <v>126.91331839999999</v>
+      </c>
       <c r="G50" s="1"/>
-      <c r="H50" s="1"/>
-      <c r="I50" s="1"/>
+      <c r="H50" s="11">
+        <v>6500</v>
+      </c>
+      <c r="I50" s="1" t="s">
+        <v>194</v>
+      </c>
       <c r="J50" s="1"/>
       <c r="K50" s="1"/>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A51" s="8"/>
-      <c r="B51" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="C51" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="D51" s="16" t="s">
-        <v>81</v>
-      </c>
-      <c r="E51" s="9">
-        <v>37.414121700000003</v>
-      </c>
-      <c r="F51" s="9">
-        <v>126.978489</v>
-      </c>
-      <c r="G51" s="8"/>
-      <c r="H51" s="12">
-        <v>9000</v>
-      </c>
-      <c r="I51" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="J51" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="K51" s="8"/>
+      <c r="A51" s="1"/>
+      <c r="B51" s="1"/>
+      <c r="C51" s="1"/>
+      <c r="D51" s="1"/>
+      <c r="E51" s="1"/>
+      <c r="F51" s="1"/>
+      <c r="G51" s="1"/>
+      <c r="H51" s="1"/>
+      <c r="I51" s="1"/>
+      <c r="J51" s="1"/>
+      <c r="K51" s="1"/>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A52" s="8"/>
       <c r="B52" s="7" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="C52" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="D52" s="8" t="s">
-        <v>80</v>
+      <c r="D52" s="16" t="s">
+        <v>81</v>
       </c>
       <c r="E52" s="9">
-        <v>37.416232999999998</v>
+        <v>37.414121700000003</v>
       </c>
       <c r="F52" s="9">
-        <v>126.97617579999999</v>
+        <v>126.978489</v>
       </c>
       <c r="G52" s="8"/>
       <c r="H52" s="12">
-        <v>8000</v>
+        <v>9000</v>
       </c>
       <c r="I52" s="8" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="J52" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="K52" s="8" t="s">
-        <v>85</v>
-      </c>
+        <v>79</v>
+      </c>
+      <c r="K52" s="8"/>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A53" s="8"/>
       <c r="B53" s="7" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C53" s="8" t="s">
         <v>76</v>
       </c>
       <c r="D53" s="8" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="E53" s="9">
-        <v>37.417220399999998</v>
+        <v>37.416232999999998</v>
       </c>
       <c r="F53" s="9">
-        <v>126.97502830000001</v>
+        <v>126.97617579999999</v>
       </c>
       <c r="G53" s="8"/>
       <c r="H53" s="12">
-        <v>8500</v>
+        <v>8000</v>
       </c>
       <c r="I53" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="J53" s="8"/>
+      <c r="J53" s="8" t="s">
+        <v>82</v>
+      </c>
       <c r="K53" s="8" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A54" s="8"/>
+      <c r="B54" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="C54" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="D54" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="E54" s="9">
+        <v>37.417220399999998</v>
+      </c>
+      <c r="F54" s="9">
+        <v>126.97502830000001</v>
+      </c>
+      <c r="G54" s="8"/>
+      <c r="H54" s="12">
+        <v>8500</v>
+      </c>
+      <c r="I54" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="J54" s="8"/>
+      <c r="K54" s="8" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A54" s="1"/>
-      <c r="B54" s="4"/>
-      <c r="C54" s="18"/>
-      <c r="D54" s="17"/>
-      <c r="E54" s="6"/>
-      <c r="F54" s="6"/>
-      <c r="G54" s="1"/>
-      <c r="H54" s="6"/>
-      <c r="I54" s="1"/>
-      <c r="J54" s="1"/>
-      <c r="K54" s="1"/>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A55" s="1"/>
-      <c r="B55" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="C55" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="D55" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="E55" s="6">
-        <v>37.461079300000002</v>
-      </c>
-      <c r="F55" s="6">
-        <v>126.87630040000001</v>
-      </c>
+      <c r="B55" s="4"/>
+      <c r="C55" s="18"/>
+      <c r="D55" s="17"/>
+      <c r="E55" s="6"/>
+      <c r="F55" s="6"/>
       <c r="G55" s="1"/>
-      <c r="H55" s="11">
-        <v>7000</v>
-      </c>
-      <c r="I55" s="1" t="s">
-        <v>156</v>
-      </c>
+      <c r="H55" s="6"/>
+      <c r="I55" s="1"/>
       <c r="J55" s="1"/>
       <c r="K55" s="1"/>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A56" s="1"/>
       <c r="B56" s="4" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>153</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="E56" s="6">
-        <v>37.4477519</v>
+        <v>37.461079300000002</v>
       </c>
       <c r="F56" s="6">
-        <v>126.89218219999999</v>
+        <v>126.87630040000001</v>
       </c>
       <c r="G56" s="1"/>
-      <c r="H56" s="6"/>
+      <c r="H56" s="11">
+        <v>7000</v>
+      </c>
       <c r="I56" s="1" t="s">
-        <v>107</v>
+        <v>156</v>
       </c>
       <c r="J56" s="1"/>
       <c r="K56" s="1"/>
@@ -2838,44 +2859,56 @@
     <row r="57" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A57" s="1"/>
       <c r="B57" s="4" t="s">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>153</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="E57" s="6">
-        <v>37.445887599999999</v>
+        <v>37.4477519</v>
       </c>
       <c r="F57" s="6">
-        <v>126.89412780000001</v>
+        <v>126.89218219999999</v>
       </c>
       <c r="G57" s="1"/>
-      <c r="H57" s="6">
-        <v>8000</v>
-      </c>
+      <c r="H57" s="6"/>
       <c r="I57" s="1" t="s">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="J57" s="1"/>
-      <c r="K57" s="1" t="s">
-        <v>168</v>
-      </c>
+      <c r="K57" s="1"/>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A58" s="1"/>
-      <c r="B58" s="4"/>
-      <c r="C58" s="1"/>
-      <c r="D58" s="1"/>
-      <c r="E58" s="6"/>
-      <c r="F58" s="6"/>
+      <c r="B58" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="E58" s="6">
+        <v>37.445887599999999</v>
+      </c>
+      <c r="F58" s="6">
+        <v>126.89412780000001</v>
+      </c>
       <c r="G58" s="1"/>
-      <c r="H58" s="6"/>
-      <c r="I58" s="1"/>
+      <c r="H58" s="6">
+        <v>8000</v>
+      </c>
+      <c r="I58" s="1" t="s">
+        <v>95</v>
+      </c>
       <c r="J58" s="1"/>
-      <c r="K58" s="1"/>
+      <c r="K58" s="1" t="s">
+        <v>168</v>
+      </c>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A59" s="1"/>
@@ -2916,6 +2949,19 @@
       <c r="J61" s="1"/>
       <c r="K61" s="1"/>
     </row>
+    <row r="62" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A62" s="1"/>
+      <c r="B62" s="4"/>
+      <c r="C62" s="1"/>
+      <c r="D62" s="1"/>
+      <c r="E62" s="6"/>
+      <c r="F62" s="6"/>
+      <c r="G62" s="1"/>
+      <c r="H62" s="6"/>
+      <c r="I62" s="1"/>
+      <c r="J62" s="1"/>
+      <c r="K62" s="1"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/restaurants.xlsx
+++ b/data/restaurants.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L1008"/>
+  <dimension ref="A1:L1156"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -38243,6 +38243,9 @@
       <c r="K996" t="str">
         <v/>
       </c>
+      <c r="L996" t="str">
+        <v/>
+      </c>
     </row>
     <row r="997">
       <c r="A997" t="str">
@@ -38278,6 +38281,9 @@
       <c r="K997" t="str">
         <v/>
       </c>
+      <c r="L997" t="str">
+        <v/>
+      </c>
     </row>
     <row r="998">
       <c r="A998" t="str">
@@ -38313,6 +38319,9 @@
       <c r="K998" t="str">
         <v/>
       </c>
+      <c r="L998" t="str">
+        <v/>
+      </c>
     </row>
     <row r="999">
       <c r="A999" t="str">
@@ -38348,6 +38357,9 @@
       <c r="K999" t="str">
         <v/>
       </c>
+      <c r="L999" t="str">
+        <v/>
+      </c>
     </row>
     <row r="1000">
       <c r="A1000" t="str">
@@ -38383,6 +38395,9 @@
       <c r="K1000" t="str">
         <v/>
       </c>
+      <c r="L1000" t="str">
+        <v/>
+      </c>
     </row>
     <row r="1001">
       <c r="A1001" t="str">
@@ -38418,6 +38433,9 @@
       <c r="K1001" t="str">
         <v/>
       </c>
+      <c r="L1001" t="str">
+        <v/>
+      </c>
     </row>
     <row r="1002">
       <c r="A1002" t="str">
@@ -38453,6 +38471,9 @@
       <c r="K1002" t="str">
         <v/>
       </c>
+      <c r="L1002" t="str">
+        <v/>
+      </c>
     </row>
     <row r="1003">
       <c r="A1003" t="str">
@@ -38488,6 +38509,9 @@
       <c r="K1003" t="str">
         <v/>
       </c>
+      <c r="L1003" t="str">
+        <v/>
+      </c>
     </row>
     <row r="1004">
       <c r="A1004" t="str">
@@ -38523,6 +38547,9 @@
       <c r="K1004" t="str">
         <v/>
       </c>
+      <c r="L1004" t="str">
+        <v/>
+      </c>
     </row>
     <row r="1005">
       <c r="A1005" t="str">
@@ -38558,6 +38585,9 @@
       <c r="K1005" t="str">
         <v/>
       </c>
+      <c r="L1005" t="str">
+        <v/>
+      </c>
     </row>
     <row r="1006">
       <c r="A1006" t="str">
@@ -38593,6 +38623,9 @@
       <c r="K1006" t="str">
         <v/>
       </c>
+      <c r="L1006" t="str">
+        <v/>
+      </c>
     </row>
     <row r="1007">
       <c r="A1007" t="str">
@@ -38628,6 +38661,9 @@
       <c r="K1007" t="str">
         <v/>
       </c>
+      <c r="L1007" t="str">
+        <v/>
+      </c>
     </row>
     <row r="1008">
       <c r="A1008" t="str">
@@ -38663,10 +38699,5637 @@
       <c r="K1008" t="str">
         <v/>
       </c>
+      <c r="L1008" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1009">
+      <c r="A1009" t="str">
+        <v/>
+      </c>
+      <c r="B1009" t="str">
+        <v>다정한식뷔페</v>
+      </c>
+      <c r="C1009" t="str">
+        <v>화성시 만세구</v>
+      </c>
+      <c r="D1009" t="str">
+        <v>경기도 화성시 만세구 송산면 화성로 600</v>
+      </c>
+      <c r="E1009" t="str">
+        <v>37.211092</v>
+      </c>
+      <c r="F1009" t="str">
+        <v>126.755095</v>
+      </c>
+      <c r="G1009" t="str">
+        <v/>
+      </c>
+      <c r="H1009" t="str">
+        <v/>
+      </c>
+      <c r="I1009" t="str">
+        <v/>
+      </c>
+      <c r="J1009" t="str">
+        <v/>
+      </c>
+      <c r="K1009" t="str">
+        <v/>
+      </c>
+      <c r="L1009" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1010">
+      <c r="A1010" t="str">
+        <v/>
+      </c>
+      <c r="B1010" t="str">
+        <v>만석한식뷔페</v>
+      </c>
+      <c r="C1010" t="str">
+        <v>화성시 만세구</v>
+      </c>
+      <c r="D1010" t="str">
+        <v>경기도 화성시 만세구 마도면 쌍송북로27번길 28-4</v>
+      </c>
+      <c r="E1010" t="str">
+        <v>37.195376</v>
+      </c>
+      <c r="F1010" t="str">
+        <v>126.786728</v>
+      </c>
+      <c r="G1010" t="str">
+        <v/>
+      </c>
+      <c r="H1010" t="str">
+        <v/>
+      </c>
+      <c r="I1010" t="str">
+        <v/>
+      </c>
+      <c r="J1010" t="str">
+        <v/>
+      </c>
+      <c r="K1010" t="str">
+        <v/>
+      </c>
+      <c r="L1010" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1011">
+      <c r="A1011" t="str">
+        <v/>
+      </c>
+      <c r="B1011" t="str">
+        <v>한백협동화주</v>
+      </c>
+      <c r="C1011" t="str">
+        <v>화성시 만세구</v>
+      </c>
+      <c r="D1011" t="str">
+        <v>경기도 화성시 만세구 마도면 쌍송북로 64-12</v>
+      </c>
+      <c r="E1011" t="str">
+        <v>37.198438</v>
+      </c>
+      <c r="F1011" t="str">
+        <v>126.790617</v>
+      </c>
+      <c r="G1011" t="str">
+        <v/>
+      </c>
+      <c r="H1011" t="str">
+        <v/>
+      </c>
+      <c r="I1011" t="str">
+        <v/>
+      </c>
+      <c r="J1011" t="str">
+        <v/>
+      </c>
+      <c r="K1011" t="str">
+        <v/>
+      </c>
+      <c r="L1011" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1012">
+      <c r="A1012" t="str">
+        <v/>
+      </c>
+      <c r="B1012" t="str">
+        <v>한식뷔페The맛</v>
+      </c>
+      <c r="C1012" t="str">
+        <v>화성시 만세구</v>
+      </c>
+      <c r="D1012" t="str">
+        <v>경기도 화성시 만세구 마도면 화성로 944</v>
+      </c>
+      <c r="E1012" t="str">
+        <v>37.201583</v>
+      </c>
+      <c r="F1012" t="str">
+        <v>126.790890</v>
+      </c>
+      <c r="G1012" t="str">
+        <v/>
+      </c>
+      <c r="H1012" t="str">
+        <v/>
+      </c>
+      <c r="I1012" t="str">
+        <v/>
+      </c>
+      <c r="J1012" t="str">
+        <v/>
+      </c>
+      <c r="K1012" t="str">
+        <v/>
+      </c>
+      <c r="L1012" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1013">
+      <c r="A1013" t="str">
+        <v/>
+      </c>
+      <c r="B1013" t="str">
+        <v>우리뷔페식당</v>
+      </c>
+      <c r="C1013" t="str">
+        <v>화성시 만세구</v>
+      </c>
+      <c r="D1013" t="str">
+        <v>경기도 화성시 만세구 마도면 송정로264번길 66</v>
+      </c>
+      <c r="E1013" t="str">
+        <v>37.218498</v>
+      </c>
+      <c r="F1013" t="str">
+        <v>126.797547</v>
+      </c>
+      <c r="G1013" t="str">
+        <v/>
+      </c>
+      <c r="H1013" t="str">
+        <v/>
+      </c>
+      <c r="I1013" t="str">
+        <v/>
+      </c>
+      <c r="J1013" t="str">
+        <v/>
+      </c>
+      <c r="K1013" t="str">
+        <v/>
+      </c>
+      <c r="L1013" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1014">
+      <c r="A1014" t="str">
+        <v/>
+      </c>
+      <c r="B1014" t="str">
+        <v>정성한식부페</v>
+      </c>
+      <c r="C1014" t="str">
+        <v>화성시 만세구</v>
+      </c>
+      <c r="D1014" t="str">
+        <v>경기도 화성시 만세구 마도면 화성로 913-15</v>
+      </c>
+      <c r="E1014" t="str">
+        <v>37.204030</v>
+      </c>
+      <c r="F1014" t="str">
+        <v>126.788698</v>
+      </c>
+      <c r="G1014" t="str">
+        <v/>
+      </c>
+      <c r="H1014" t="str">
+        <v/>
+      </c>
+      <c r="I1014" t="str">
+        <v/>
+      </c>
+      <c r="J1014" t="str">
+        <v/>
+      </c>
+      <c r="K1014" t="str">
+        <v/>
+      </c>
+      <c r="L1014" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1015">
+      <c r="A1015" t="str">
+        <v/>
+      </c>
+      <c r="B1015" t="str">
+        <v>진수성찬</v>
+      </c>
+      <c r="C1015" t="str">
+        <v>화성시 만세구</v>
+      </c>
+      <c r="D1015" t="str">
+        <v>경기도 화성시 만세구 남양읍 남양성지로 89</v>
+      </c>
+      <c r="E1015" t="str">
+        <v>37.207468</v>
+      </c>
+      <c r="F1015" t="str">
+        <v>126.813528</v>
+      </c>
+      <c r="G1015" t="str">
+        <v/>
+      </c>
+      <c r="H1015" t="str">
+        <v/>
+      </c>
+      <c r="I1015" t="str">
+        <v/>
+      </c>
+      <c r="J1015" t="str">
+        <v/>
+      </c>
+      <c r="K1015" t="str">
+        <v/>
+      </c>
+      <c r="L1015" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1016">
+      <c r="A1016" t="str">
+        <v/>
+      </c>
+      <c r="B1016" t="str">
+        <v>든든한식뷔페</v>
+      </c>
+      <c r="C1016" t="str">
+        <v>화성시 만세구</v>
+      </c>
+      <c r="D1016" t="str">
+        <v>경기도 화성시 만세구 마도면 마도로 727</v>
+      </c>
+      <c r="E1016" t="str">
+        <v>37.190484</v>
+      </c>
+      <c r="F1016" t="str">
+        <v>126.782124</v>
+      </c>
+      <c r="G1016" t="str">
+        <v/>
+      </c>
+      <c r="H1016" t="str">
+        <v/>
+      </c>
+      <c r="I1016" t="str">
+        <v/>
+      </c>
+      <c r="J1016" t="str">
+        <v/>
+      </c>
+      <c r="K1016" t="str">
+        <v/>
+      </c>
+      <c r="L1016" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1017">
+      <c r="A1017" t="str">
+        <v/>
+      </c>
+      <c r="B1017" t="str">
+        <v>민지한식부페</v>
+      </c>
+      <c r="C1017" t="str">
+        <v>화성시 만세구</v>
+      </c>
+      <c r="D1017" t="str">
+        <v>경기도 화성시 만세구 송산면 삼존로 59</v>
+      </c>
+      <c r="E1017" t="str">
+        <v>37.216233</v>
+      </c>
+      <c r="F1017" t="str">
+        <v>126.762030</v>
+      </c>
+      <c r="G1017" t="str">
+        <v/>
+      </c>
+      <c r="H1017" t="str">
+        <v/>
+      </c>
+      <c r="I1017" t="str">
+        <v/>
+      </c>
+      <c r="J1017" t="str">
+        <v/>
+      </c>
+      <c r="K1017" t="str">
+        <v/>
+      </c>
+      <c r="L1017" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1018">
+      <c r="A1018" t="str">
+        <v/>
+      </c>
+      <c r="B1018" t="str">
+        <v>도담한식뷔페</v>
+      </c>
+      <c r="C1018" t="str">
+        <v>화성시 병점구</v>
+      </c>
+      <c r="D1018" t="str">
+        <v>경기도 화성시 병점구 삼성1로6길 27</v>
+      </c>
+      <c r="E1018" t="str">
+        <v>37.228082</v>
+      </c>
+      <c r="F1018" t="str">
+        <v>127.073908</v>
+      </c>
+      <c r="G1018" t="str">
+        <v/>
+      </c>
+      <c r="H1018" t="str">
+        <v/>
+      </c>
+      <c r="I1018" t="str">
+        <v/>
+      </c>
+      <c r="J1018" t="str">
+        <v/>
+      </c>
+      <c r="K1018" t="str">
+        <v/>
+      </c>
+      <c r="L1018" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1019">
+      <c r="A1019" t="str">
+        <v/>
+      </c>
+      <c r="B1019" t="str">
+        <v>공간한식뷔페</v>
+      </c>
+      <c r="C1019" t="str">
+        <v>화성시 병점구</v>
+      </c>
+      <c r="D1019" t="str">
+        <v>경기도 화성시 병점구 삼성1로6길 29-9</v>
+      </c>
+      <c r="E1019" t="str">
+        <v>37.228749</v>
+      </c>
+      <c r="F1019" t="str">
+        <v>127.073131</v>
+      </c>
+      <c r="G1019" t="str">
+        <v/>
+      </c>
+      <c r="H1019" t="str">
+        <v/>
+      </c>
+      <c r="I1019" t="str">
+        <v/>
+      </c>
+      <c r="J1019" t="str">
+        <v/>
+      </c>
+      <c r="K1019" t="str">
+        <v/>
+      </c>
+      <c r="L1019" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1020">
+      <c r="A1020" t="str">
+        <v/>
+      </c>
+      <c r="B1020" t="str">
+        <v>삼성웰스토리SR5Cafeteria</v>
+      </c>
+      <c r="C1020" t="str">
+        <v>용인시 기흥구</v>
+      </c>
+      <c r="D1020" t="str">
+        <v>경기도 용인시 기흥구 삼성로 1</v>
+      </c>
+      <c r="E1020" t="str">
+        <v>37.226937</v>
+      </c>
+      <c r="F1020" t="str">
+        <v>127.087767</v>
+      </c>
+      <c r="G1020" t="str">
+        <v/>
+      </c>
+      <c r="H1020" t="str">
+        <v/>
+      </c>
+      <c r="I1020" t="str">
+        <v/>
+      </c>
+      <c r="J1020" t="str">
+        <v/>
+      </c>
+      <c r="K1020" t="str">
+        <v/>
+      </c>
+      <c r="L1020" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1021">
+      <c r="A1021" t="str">
+        <v/>
+      </c>
+      <c r="B1021" t="str">
+        <v>아워홈한양디지텍</v>
+      </c>
+      <c r="C1021" t="str">
+        <v>화성시 병점구</v>
+      </c>
+      <c r="D1021" t="str">
+        <v>경기도 화성시 병점구 삼성1로 332-7</v>
+      </c>
+      <c r="E1021" t="str">
+        <v>37.232230</v>
+      </c>
+      <c r="F1021" t="str">
+        <v>127.068120</v>
+      </c>
+      <c r="G1021" t="str">
+        <v/>
+      </c>
+      <c r="H1021" t="str">
+        <v/>
+      </c>
+      <c r="I1021" t="str">
+        <v/>
+      </c>
+      <c r="J1021" t="str">
+        <v/>
+      </c>
+      <c r="K1021" t="str">
+        <v/>
+      </c>
+      <c r="L1021" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1022">
+      <c r="A1022" t="str">
+        <v/>
+      </c>
+      <c r="B1022" t="str">
+        <v>아워홈바텍</v>
+      </c>
+      <c r="C1022" t="str">
+        <v>화성시 동탄구</v>
+      </c>
+      <c r="D1022" t="str">
+        <v>경기도 화성시 동탄구 삼성1로2길 13</v>
+      </c>
+      <c r="E1022" t="str">
+        <v>37.221044</v>
+      </c>
+      <c r="F1022" t="str">
+        <v>127.075253</v>
+      </c>
+      <c r="G1022" t="str">
+        <v/>
+      </c>
+      <c r="H1022" t="str">
+        <v/>
+      </c>
+      <c r="I1022" t="str">
+        <v/>
+      </c>
+      <c r="J1022" t="str">
+        <v/>
+      </c>
+      <c r="K1022" t="str">
+        <v/>
+      </c>
+      <c r="L1022" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1023">
+      <c r="A1023" t="str">
+        <v/>
+      </c>
+      <c r="B1023" t="str">
+        <v>남도한식뷔페</v>
+      </c>
+      <c r="C1023" t="str">
+        <v>화성시 병점구</v>
+      </c>
+      <c r="D1023" t="str">
+        <v>경기도 화성시 병점구 삼성1로6길 15-2</v>
+      </c>
+      <c r="E1023" t="str">
+        <v>37.228182</v>
+      </c>
+      <c r="F1023" t="str">
+        <v>127.072827</v>
+      </c>
+      <c r="G1023" t="str">
+        <v/>
+      </c>
+      <c r="H1023" t="str">
+        <v/>
+      </c>
+      <c r="I1023" t="str">
+        <v/>
+      </c>
+      <c r="J1023" t="str">
+        <v/>
+      </c>
+      <c r="K1023" t="str">
+        <v/>
+      </c>
+      <c r="L1023" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1024">
+      <c r="A1024" t="str">
+        <v/>
+      </c>
+      <c r="B1024" t="str">
+        <v>더쉐프한식뷔페</v>
+      </c>
+      <c r="C1024" t="str">
+        <v>화성시 동탄구</v>
+      </c>
+      <c r="D1024" t="str">
+        <v>경기도 화성시 동탄구 삼성1로 209</v>
+      </c>
+      <c r="E1024" t="str">
+        <v>37.221855</v>
+      </c>
+      <c r="F1024" t="str">
+        <v>127.074916</v>
+      </c>
+      <c r="G1024" t="str">
+        <v/>
+      </c>
+      <c r="H1024" t="str">
+        <v/>
+      </c>
+      <c r="I1024" t="str">
+        <v/>
+      </c>
+      <c r="J1024" t="str">
+        <v/>
+      </c>
+      <c r="K1024" t="str">
+        <v/>
+      </c>
+      <c r="L1024" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1025">
+      <c r="A1025" t="str">
+        <v/>
+      </c>
+      <c r="B1025" t="str">
+        <v>동성한식뷔페</v>
+      </c>
+      <c r="C1025" t="str">
+        <v>화성시 병점구</v>
+      </c>
+      <c r="D1025" t="str">
+        <v>경기도 화성시 병점구 효행로 1362-9</v>
+      </c>
+      <c r="E1025" t="str">
+        <v>37.229132</v>
+      </c>
+      <c r="F1025" t="str">
+        <v>127.065762</v>
+      </c>
+      <c r="G1025" t="str">
+        <v/>
+      </c>
+      <c r="H1025" t="str">
+        <v/>
+      </c>
+      <c r="I1025" t="str">
+        <v/>
+      </c>
+      <c r="J1025" t="str">
+        <v/>
+      </c>
+      <c r="K1025" t="str">
+        <v/>
+      </c>
+      <c r="L1025" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1026">
+      <c r="A1026" t="str">
+        <v/>
+      </c>
+      <c r="B1026" t="str">
+        <v>현대그린푸드서한연구소</v>
+      </c>
+      <c r="C1026" t="str">
+        <v>화성시 동탄구</v>
+      </c>
+      <c r="D1026" t="str">
+        <v>경기도 화성시 동탄구 삼성1로5길 49</v>
+      </c>
+      <c r="E1026" t="str">
+        <v>37.222615</v>
+      </c>
+      <c r="F1026" t="str">
+        <v>127.069531</v>
+      </c>
+      <c r="G1026" t="str">
+        <v/>
+      </c>
+      <c r="H1026" t="str">
+        <v/>
+      </c>
+      <c r="I1026" t="str">
+        <v/>
+      </c>
+      <c r="J1026" t="str">
+        <v/>
+      </c>
+      <c r="K1026" t="str">
+        <v/>
+      </c>
+      <c r="L1026" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1027">
+      <c r="A1027" t="str">
+        <v/>
+      </c>
+      <c r="B1027" t="str">
+        <v>남도한식뷔페</v>
+      </c>
+      <c r="C1027" t="str">
+        <v>용인시 기흥구</v>
+      </c>
+      <c r="D1027" t="str">
+        <v>경기도 용인시 기흥구 농서로 68</v>
+      </c>
+      <c r="E1027" t="str">
+        <v>37.223727</v>
+      </c>
+      <c r="F1027" t="str">
+        <v>127.090614</v>
+      </c>
+      <c r="G1027" t="str">
+        <v/>
+      </c>
+      <c r="H1027" t="str">
+        <v/>
+      </c>
+      <c r="I1027" t="str">
+        <v/>
+      </c>
+      <c r="J1027" t="str">
+        <v/>
+      </c>
+      <c r="K1027" t="str">
+        <v/>
+      </c>
+      <c r="L1027" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1028">
+      <c r="A1028" t="str">
+        <v/>
+      </c>
+      <c r="B1028" t="str">
+        <v>삼성웰스토리전자기흥주</v>
+      </c>
+      <c r="C1028" t="str">
+        <v>용인시 기흥구</v>
+      </c>
+      <c r="D1028" t="str">
+        <v>경기도 용인시 기흥구 삼성로 1</v>
+      </c>
+      <c r="E1028" t="str">
+        <v>37.226937</v>
+      </c>
+      <c r="F1028" t="str">
+        <v>127.087767</v>
+      </c>
+      <c r="G1028" t="str">
+        <v/>
+      </c>
+      <c r="H1028" t="str">
+        <v/>
+      </c>
+      <c r="I1028" t="str">
+        <v/>
+      </c>
+      <c r="J1028" t="str">
+        <v/>
+      </c>
+      <c r="K1028" t="str">
+        <v/>
+      </c>
+      <c r="L1028" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1029">
+      <c r="A1029" t="str">
+        <v/>
+      </c>
+      <c r="B1029" t="str">
+        <v>농서한식뷔페</v>
+      </c>
+      <c r="C1029" t="str">
+        <v>용인시 기흥구</v>
+      </c>
+      <c r="D1029" t="str">
+        <v>경기도 용인시 기흥구 농서로 236</v>
+      </c>
+      <c r="E1029" t="str">
+        <v>37.228352</v>
+      </c>
+      <c r="F1029" t="str">
+        <v>127.074461</v>
+      </c>
+      <c r="G1029" t="str">
+        <v/>
+      </c>
+      <c r="H1029" t="str">
+        <v/>
+      </c>
+      <c r="I1029" t="str">
+        <v/>
+      </c>
+      <c r="J1029" t="str">
+        <v/>
+      </c>
+      <c r="K1029" t="str">
+        <v/>
+      </c>
+      <c r="L1029" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1030">
+      <c r="A1030" t="str">
+        <v/>
+      </c>
+      <c r="B1030" t="str">
+        <v>삼성웰스토리3M기술연구소</v>
+      </c>
+      <c r="C1030" t="str">
+        <v>화성시 동탄구</v>
+      </c>
+      <c r="D1030" t="str">
+        <v>경기도 화성시 동탄구 삼성1로5길 7</v>
+      </c>
+      <c r="E1030" t="str">
+        <v>37.224235</v>
+      </c>
+      <c r="F1030" t="str">
+        <v>127.072406</v>
+      </c>
+      <c r="G1030" t="str">
+        <v/>
+      </c>
+      <c r="H1030" t="str">
+        <v/>
+      </c>
+      <c r="I1030" t="str">
+        <v/>
+      </c>
+      <c r="J1030" t="str">
+        <v/>
+      </c>
+      <c r="K1030" t="str">
+        <v/>
+      </c>
+      <c r="L1030" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1031">
+      <c r="A1031" t="str">
+        <v/>
+      </c>
+      <c r="B1031" t="str">
+        <v>화성뷔폐식당</v>
+      </c>
+      <c r="C1031" t="str">
+        <v>화성시 병점구</v>
+      </c>
+      <c r="D1031" t="str">
+        <v>경기도 화성시 병점구 반월길 16</v>
+      </c>
+      <c r="E1031" t="str">
+        <v>37.228593</v>
+      </c>
+      <c r="F1031" t="str">
+        <v>127.063125</v>
+      </c>
+      <c r="G1031" t="str">
+        <v/>
+      </c>
+      <c r="H1031" t="str">
+        <v/>
+      </c>
+      <c r="I1031" t="str">
+        <v/>
+      </c>
+      <c r="J1031" t="str">
+        <v/>
+      </c>
+      <c r="K1031" t="str">
+        <v/>
+      </c>
+      <c r="L1031" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1032">
+      <c r="A1032" t="str">
+        <v/>
+      </c>
+      <c r="B1032" t="str">
+        <v>한식명가부페</v>
+      </c>
+      <c r="C1032" t="str">
+        <v>화성시 동탄구</v>
+      </c>
+      <c r="D1032" t="str">
+        <v>경기도 화성시 동탄구 삼성1로 209</v>
+      </c>
+      <c r="E1032" t="str">
+        <v>37.221855</v>
+      </c>
+      <c r="F1032" t="str">
+        <v>127.074916</v>
+      </c>
+      <c r="G1032" t="str">
+        <v/>
+      </c>
+      <c r="H1032" t="str">
+        <v/>
+      </c>
+      <c r="I1032" t="str">
+        <v/>
+      </c>
+      <c r="J1032" t="str">
+        <v/>
+      </c>
+      <c r="K1032" t="str">
+        <v/>
+      </c>
+      <c r="L1032" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1033">
+      <c r="A1033" t="str">
+        <v/>
+      </c>
+      <c r="B1033" t="str">
+        <v>삼성웰스토리남자기숙사Cafeteria</v>
+      </c>
+      <c r="C1033" t="str">
+        <v>용인시 기흥구</v>
+      </c>
+      <c r="D1033" t="str">
+        <v>경기도 용인시 기흥구 삼성로 1</v>
+      </c>
+      <c r="E1033" t="str">
+        <v>37.226937</v>
+      </c>
+      <c r="F1033" t="str">
+        <v>127.087767</v>
+      </c>
+      <c r="G1033" t="str">
+        <v/>
+      </c>
+      <c r="H1033" t="str">
+        <v/>
+      </c>
+      <c r="I1033" t="str">
+        <v/>
+      </c>
+      <c r="J1033" t="str">
+        <v/>
+      </c>
+      <c r="K1033" t="str">
+        <v/>
+      </c>
+      <c r="L1033" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1034">
+      <c r="A1034" t="str">
+        <v/>
+      </c>
+      <c r="B1034" t="str">
+        <v>삼성웰스토리16라인Cafeteria</v>
+      </c>
+      <c r="C1034" t="str">
+        <v>화성시 병점구</v>
+      </c>
+      <c r="D1034" t="str">
+        <v>경기도 화성시 병점구 삼성전자로 1</v>
+      </c>
+      <c r="E1034" t="str">
+        <v>37.223475</v>
+      </c>
+      <c r="F1034" t="str">
+        <v>127.063335</v>
+      </c>
+      <c r="G1034" t="str">
+        <v/>
+      </c>
+      <c r="H1034" t="str">
+        <v/>
+      </c>
+      <c r="I1034" t="str">
+        <v/>
+      </c>
+      <c r="J1034" t="str">
+        <v/>
+      </c>
+      <c r="K1034" t="str">
+        <v/>
+      </c>
+      <c r="L1034" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1035">
+      <c r="A1035" t="str">
+        <v/>
+      </c>
+      <c r="B1035" t="str">
+        <v>아워홈삼성전자화성MR2점</v>
+      </c>
+      <c r="C1035" t="str">
+        <v>화성시 병점구</v>
+      </c>
+      <c r="D1035" t="str">
+        <v>경기도 화성시 병점구 삼성전자로 1</v>
+      </c>
+      <c r="E1035" t="str">
+        <v>37.223466</v>
+      </c>
+      <c r="F1035" t="str">
+        <v>127.063346</v>
+      </c>
+      <c r="G1035" t="str">
+        <v/>
+      </c>
+      <c r="H1035" t="str">
+        <v/>
+      </c>
+      <c r="I1035" t="str">
+        <v/>
+      </c>
+      <c r="J1035" t="str">
+        <v/>
+      </c>
+      <c r="K1035" t="str">
+        <v/>
+      </c>
+      <c r="L1035" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1036">
+      <c r="A1036" t="str">
+        <v/>
+      </c>
+      <c r="B1036" t="str">
+        <v>수라에프앤씨주</v>
+      </c>
+      <c r="C1036" t="str">
+        <v>용인시 기흥구</v>
+      </c>
+      <c r="D1036" t="str">
+        <v>경기도 용인시 기흥구 서천동로83번길 18</v>
+      </c>
+      <c r="E1036" t="str">
+        <v>37.233012</v>
+      </c>
+      <c r="F1036" t="str">
+        <v>127.072324</v>
+      </c>
+      <c r="G1036" t="str">
+        <v/>
+      </c>
+      <c r="H1036" t="str">
+        <v/>
+      </c>
+      <c r="I1036" t="str">
+        <v/>
+      </c>
+      <c r="J1036" t="str">
+        <v/>
+      </c>
+      <c r="K1036" t="str">
+        <v/>
+      </c>
+      <c r="L1036" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1037">
+      <c r="A1037" t="str">
+        <v/>
+      </c>
+      <c r="B1037" t="str">
+        <v>이에이치푸드</v>
+      </c>
+      <c r="C1037" t="str">
+        <v>용인시 기흥구</v>
+      </c>
+      <c r="D1037" t="str">
+        <v>경기도 용인시 기흥구 삼성로 1</v>
+      </c>
+      <c r="E1037" t="str">
+        <v>37.226937</v>
+      </c>
+      <c r="F1037" t="str">
+        <v>127.087767</v>
+      </c>
+      <c r="G1037" t="str">
+        <v/>
+      </c>
+      <c r="H1037" t="str">
+        <v/>
+      </c>
+      <c r="I1037" t="str">
+        <v/>
+      </c>
+      <c r="J1037" t="str">
+        <v/>
+      </c>
+      <c r="K1037" t="str">
+        <v/>
+      </c>
+      <c r="L1037" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1038">
+      <c r="A1038" t="str">
+        <v/>
+      </c>
+      <c r="B1038" t="str">
+        <v>우리한식부페</v>
+      </c>
+      <c r="C1038" t="str">
+        <v>화성시 병점구</v>
+      </c>
+      <c r="D1038" t="str">
+        <v>경기도 화성시 병점구 효행로 1318-3</v>
+      </c>
+      <c r="E1038" t="str">
+        <v>37.225249</v>
+      </c>
+      <c r="F1038" t="str">
+        <v>127.064226</v>
+      </c>
+      <c r="G1038" t="str">
+        <v/>
+      </c>
+      <c r="H1038" t="str">
+        <v/>
+      </c>
+      <c r="I1038" t="str">
+        <v/>
+      </c>
+      <c r="J1038" t="str">
+        <v/>
+      </c>
+      <c r="K1038" t="str">
+        <v/>
+      </c>
+      <c r="L1038" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1039">
+      <c r="A1039" t="str">
+        <v/>
+      </c>
+      <c r="B1039" t="str">
+        <v>레몬푸드주</v>
+      </c>
+      <c r="C1039" t="str">
+        <v>화성시 병점구</v>
+      </c>
+      <c r="D1039" t="str">
+        <v>경기도 화성시 병점구 영통로27번길 53</v>
+      </c>
+      <c r="E1039" t="str">
+        <v>37.232038</v>
+      </c>
+      <c r="F1039" t="str">
+        <v>127.057403</v>
+      </c>
+      <c r="G1039" t="str">
+        <v/>
+      </c>
+      <c r="H1039" t="str">
+        <v/>
+      </c>
+      <c r="I1039" t="str">
+        <v/>
+      </c>
+      <c r="J1039" t="str">
+        <v/>
+      </c>
+      <c r="K1039" t="str">
+        <v/>
+      </c>
+      <c r="L1039" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1040">
+      <c r="A1040" t="str">
+        <v/>
+      </c>
+      <c r="B1040" t="str">
+        <v>고메드갤러리아대한항공배구단</v>
+      </c>
+      <c r="C1040" t="str">
+        <v>용인시 기흥구</v>
+      </c>
+      <c r="D1040" t="str">
+        <v>경기도 용인시 기흥구 기곡로 81-18</v>
+      </c>
+      <c r="E1040" t="str">
+        <v>37.246015</v>
+      </c>
+      <c r="F1040" t="str">
+        <v>127.096377</v>
+      </c>
+      <c r="G1040" t="str">
+        <v/>
+      </c>
+      <c r="H1040" t="str">
+        <v/>
+      </c>
+      <c r="I1040" t="str">
+        <v/>
+      </c>
+      <c r="J1040" t="str">
+        <v/>
+      </c>
+      <c r="K1040" t="str">
+        <v/>
+      </c>
+      <c r="L1040" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1041">
+      <c r="A1041" t="str">
+        <v/>
+      </c>
+      <c r="B1041" t="str">
+        <v>콩스</v>
+      </c>
+      <c r="C1041" t="str">
+        <v>용인시 기흥구</v>
+      </c>
+      <c r="D1041" t="str">
+        <v>경기도 용인시 기흥구 덕영대로 1732</v>
+      </c>
+      <c r="E1041" t="str">
+        <v>37.239800</v>
+      </c>
+      <c r="F1041" t="str">
+        <v>127.081200</v>
+      </c>
+      <c r="G1041" t="str">
+        <v/>
+      </c>
+      <c r="H1041" t="str">
+        <v/>
+      </c>
+      <c r="I1041" t="str">
+        <v/>
+      </c>
+      <c r="J1041" t="str">
+        <v/>
+      </c>
+      <c r="K1041" t="str">
+        <v/>
+      </c>
+      <c r="L1041" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1042">
+      <c r="A1042" t="str">
+        <v/>
+      </c>
+      <c r="B1042" t="str">
+        <v>이피엠식당</v>
+      </c>
+      <c r="C1042" t="str">
+        <v>화성시 동탄구</v>
+      </c>
+      <c r="D1042" t="str">
+        <v>경기도 화성시 동탄구 삼성1로3길 56</v>
+      </c>
+      <c r="E1042" t="str">
+        <v>37.221200</v>
+      </c>
+      <c r="F1042" t="str">
+        <v>127.070048</v>
+      </c>
+      <c r="G1042" t="str">
+        <v/>
+      </c>
+      <c r="H1042" t="str">
+        <v/>
+      </c>
+      <c r="I1042" t="str">
+        <v/>
+      </c>
+      <c r="J1042" t="str">
+        <v/>
+      </c>
+      <c r="K1042" t="str">
+        <v/>
+      </c>
+      <c r="L1042" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1043">
+      <c r="A1043" t="str">
+        <v/>
+      </c>
+      <c r="B1043" t="str">
+        <v>까페테리아</v>
+      </c>
+      <c r="C1043" t="str">
+        <v>화성시 동탄구</v>
+      </c>
+      <c r="D1043" t="str">
+        <v>경기도 화성시 동탄구 삼성1로4길 49</v>
+      </c>
+      <c r="E1043" t="str">
+        <v>37.221606</v>
+      </c>
+      <c r="F1043" t="str">
+        <v>127.069801</v>
+      </c>
+      <c r="G1043" t="str">
+        <v/>
+      </c>
+      <c r="H1043" t="str">
+        <v/>
+      </c>
+      <c r="I1043" t="str">
+        <v/>
+      </c>
+      <c r="J1043" t="str">
+        <v/>
+      </c>
+      <c r="K1043" t="str">
+        <v/>
+      </c>
+      <c r="L1043" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1044">
+      <c r="A1044" t="str">
+        <v/>
+      </c>
+      <c r="B1044" t="str">
+        <v>아워홈두산중공업주</v>
+      </c>
+      <c r="C1044" t="str">
+        <v>화성시 동탄구</v>
+      </c>
+      <c r="D1044" t="str">
+        <v>경기도 화성시 동탄구 삼성1로5길 37</v>
+      </c>
+      <c r="E1044" t="str">
+        <v>37.223354</v>
+      </c>
+      <c r="F1044" t="str">
+        <v>127.070478</v>
+      </c>
+      <c r="G1044" t="str">
+        <v/>
+      </c>
+      <c r="H1044" t="str">
+        <v/>
+      </c>
+      <c r="I1044" t="str">
+        <v/>
+      </c>
+      <c r="J1044" t="str">
+        <v/>
+      </c>
+      <c r="K1044" t="str">
+        <v/>
+      </c>
+      <c r="L1044" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1045">
+      <c r="A1045" t="str">
+        <v/>
+      </c>
+      <c r="B1045" t="str">
+        <v>예담한식부페</v>
+      </c>
+      <c r="C1045" t="str">
+        <v>화성시 병점구</v>
+      </c>
+      <c r="D1045" t="str">
+        <v>경기도 화성시 병점구 효행로 1369-4</v>
+      </c>
+      <c r="E1045" t="str">
+        <v>37.229502</v>
+      </c>
+      <c r="F1045" t="str">
+        <v>127.064444</v>
+      </c>
+      <c r="G1045" t="str">
+        <v/>
+      </c>
+      <c r="H1045" t="str">
+        <v/>
+      </c>
+      <c r="I1045" t="str">
+        <v/>
+      </c>
+      <c r="J1045" t="str">
+        <v/>
+      </c>
+      <c r="K1045" t="str">
+        <v/>
+      </c>
+      <c r="L1045" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1046">
+      <c r="A1046" t="str">
+        <v/>
+      </c>
+      <c r="B1046" t="str">
+        <v>동원홈푸드신성전자정밀화성</v>
+      </c>
+      <c r="C1046" t="str">
+        <v>화성시 동탄구</v>
+      </c>
+      <c r="D1046" t="str">
+        <v>경기도 화성시 동탄구 삼성1로2길 36</v>
+      </c>
+      <c r="E1046" t="str">
+        <v>37.220974</v>
+      </c>
+      <c r="F1046" t="str">
+        <v>127.071817</v>
+      </c>
+      <c r="G1046" t="str">
+        <v/>
+      </c>
+      <c r="H1046" t="str">
+        <v/>
+      </c>
+      <c r="I1046" t="str">
+        <v/>
+      </c>
+      <c r="J1046" t="str">
+        <v/>
+      </c>
+      <c r="K1046" t="str">
+        <v/>
+      </c>
+      <c r="L1046" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1047">
+      <c r="A1047" t="str">
+        <v/>
+      </c>
+      <c r="B1047" t="str">
+        <v>고메드갤러리아대한항공신갈연수원</v>
+      </c>
+      <c r="C1047" t="str">
+        <v>용인시 기흥구</v>
+      </c>
+      <c r="D1047" t="str">
+        <v>경기도 용인시 기흥구 기곡로 81-18</v>
+      </c>
+      <c r="E1047" t="str">
+        <v>37.246015</v>
+      </c>
+      <c r="F1047" t="str">
+        <v>127.096377</v>
+      </c>
+      <c r="G1047" t="str">
+        <v/>
+      </c>
+      <c r="H1047" t="str">
+        <v/>
+      </c>
+      <c r="I1047" t="str">
+        <v/>
+      </c>
+      <c r="J1047" t="str">
+        <v/>
+      </c>
+      <c r="K1047" t="str">
+        <v/>
+      </c>
+      <c r="L1047" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1048">
+      <c r="A1048" t="str">
+        <v/>
+      </c>
+      <c r="B1048" t="str">
+        <v>꾸이한끼경희대국제캠퍼스점</v>
+      </c>
+      <c r="C1048" t="str">
+        <v>용인시 기흥구</v>
+      </c>
+      <c r="D1048" t="str">
+        <v>경기도 용인시 기흥구 덕영대로 1732</v>
+      </c>
+      <c r="E1048" t="str">
+        <v>37.239800</v>
+      </c>
+      <c r="F1048" t="str">
+        <v>127.081200</v>
+      </c>
+      <c r="G1048" t="str">
+        <v/>
+      </c>
+      <c r="H1048" t="str">
+        <v/>
+      </c>
+      <c r="I1048" t="str">
+        <v/>
+      </c>
+      <c r="J1048" t="str">
+        <v/>
+      </c>
+      <c r="K1048" t="str">
+        <v/>
+      </c>
+      <c r="L1048" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1049">
+      <c r="A1049" t="str">
+        <v/>
+      </c>
+      <c r="B1049" t="str">
+        <v>동원홈푸드엠케이피</v>
+      </c>
+      <c r="C1049" t="str">
+        <v>화성시 동탄구</v>
+      </c>
+      <c r="D1049" t="str">
+        <v>경기도 화성시 동탄구 삼성1로1길 40</v>
+      </c>
+      <c r="E1049" t="str">
+        <v>37.219109</v>
+      </c>
+      <c r="F1049" t="str">
+        <v>127.071883</v>
+      </c>
+      <c r="G1049" t="str">
+        <v/>
+      </c>
+      <c r="H1049" t="str">
+        <v/>
+      </c>
+      <c r="I1049" t="str">
+        <v/>
+      </c>
+      <c r="J1049" t="str">
+        <v/>
+      </c>
+      <c r="K1049" t="str">
+        <v/>
+      </c>
+      <c r="L1049" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1050">
+      <c r="A1050" t="str">
+        <v/>
+      </c>
+      <c r="B1050" t="str">
+        <v>삼성웰스토리TheUniverSECafeteria</v>
+      </c>
+      <c r="C1050" t="str">
+        <v>용인시 기흥구</v>
+      </c>
+      <c r="D1050" t="str">
+        <v>경기도 용인시 기흥구 서천동로 59</v>
+      </c>
+      <c r="E1050" t="str">
+        <v>37.234585</v>
+      </c>
+      <c r="F1050" t="str">
+        <v>127.078377</v>
+      </c>
+      <c r="G1050" t="str">
+        <v/>
+      </c>
+      <c r="H1050" t="str">
+        <v/>
+      </c>
+      <c r="I1050" t="str">
+        <v/>
+      </c>
+      <c r="J1050" t="str">
+        <v/>
+      </c>
+      <c r="K1050" t="str">
+        <v/>
+      </c>
+      <c r="L1050" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1051">
+      <c r="A1051" t="str">
+        <v/>
+      </c>
+      <c r="B1051" t="str">
+        <v>행복구내식당</v>
+      </c>
+      <c r="C1051" t="str">
+        <v>화성시 병점구</v>
+      </c>
+      <c r="D1051" t="str">
+        <v>경기도 화성시 병점구 반월남길62번길 26-15</v>
+      </c>
+      <c r="E1051" t="str">
+        <v>37.227731</v>
+      </c>
+      <c r="F1051" t="str">
+        <v>127.057400</v>
+      </c>
+      <c r="G1051" t="str">
+        <v/>
+      </c>
+      <c r="H1051" t="str">
+        <v/>
+      </c>
+      <c r="I1051" t="str">
+        <v/>
+      </c>
+      <c r="J1051" t="str">
+        <v/>
+      </c>
+      <c r="K1051" t="str">
+        <v/>
+      </c>
+      <c r="L1051" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1052">
+      <c r="A1052" t="str">
+        <v/>
+      </c>
+      <c r="B1052" t="str">
+        <v>탑한식뷔페</v>
+      </c>
+      <c r="C1052" t="str">
+        <v>화성시 병점구</v>
+      </c>
+      <c r="D1052" t="str">
+        <v>경기도 화성시 병점구 반월남길 6</v>
+      </c>
+      <c r="E1052" t="str">
+        <v>37.224457</v>
+      </c>
+      <c r="F1052" t="str">
+        <v>127.062851</v>
+      </c>
+      <c r="G1052" t="str">
+        <v/>
+      </c>
+      <c r="H1052" t="str">
+        <v/>
+      </c>
+      <c r="I1052" t="str">
+        <v/>
+      </c>
+      <c r="J1052" t="str">
+        <v/>
+      </c>
+      <c r="K1052" t="str">
+        <v/>
+      </c>
+      <c r="L1052" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1053">
+      <c r="A1053" t="str">
+        <v/>
+      </c>
+      <c r="B1053" t="str">
+        <v>춘향골한식뷔페</v>
+      </c>
+      <c r="C1053" t="str">
+        <v>용인시 기흥구</v>
+      </c>
+      <c r="D1053" t="str">
+        <v>경기도 용인시 기흥구 서천로201번길 14</v>
+      </c>
+      <c r="E1053" t="str">
+        <v>37.230030</v>
+      </c>
+      <c r="F1053" t="str">
+        <v>127.071803</v>
+      </c>
+      <c r="G1053" t="str">
+        <v/>
+      </c>
+      <c r="H1053" t="str">
+        <v/>
+      </c>
+      <c r="I1053" t="str">
+        <v/>
+      </c>
+      <c r="J1053" t="str">
+        <v/>
+      </c>
+      <c r="K1053" t="str">
+        <v/>
+      </c>
+      <c r="L1053" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1054">
+      <c r="A1054" t="str">
+        <v/>
+      </c>
+      <c r="B1054" t="str">
+        <v>진수캐더링</v>
+      </c>
+      <c r="C1054" t="str">
+        <v>용인시 기흥구</v>
+      </c>
+      <c r="D1054" t="str">
+        <v>경기도 용인시 기흥구 농서로153번길 8</v>
+      </c>
+      <c r="E1054" t="str">
+        <v>37.224195</v>
+      </c>
+      <c r="F1054" t="str">
+        <v>127.079381</v>
+      </c>
+      <c r="G1054" t="str">
+        <v/>
+      </c>
+      <c r="H1054" t="str">
+        <v/>
+      </c>
+      <c r="I1054" t="str">
+        <v/>
+      </c>
+      <c r="J1054" t="str">
+        <v/>
+      </c>
+      <c r="K1054" t="str">
+        <v/>
+      </c>
+      <c r="L1054" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1055">
+      <c r="A1055" t="str">
+        <v/>
+      </c>
+      <c r="B1055" t="str">
+        <v>아워홈노블카운티</v>
+      </c>
+      <c r="C1055" t="str">
+        <v>용인시 기흥구</v>
+      </c>
+      <c r="D1055" t="str">
+        <v>경기도 용인시 기흥구 덕영대로 1751</v>
+      </c>
+      <c r="E1055" t="str">
+        <v>37.253314</v>
+      </c>
+      <c r="F1055" t="str">
+        <v>127.083875</v>
+      </c>
+      <c r="G1055" t="str">
+        <v/>
+      </c>
+      <c r="H1055" t="str">
+        <v/>
+      </c>
+      <c r="I1055" t="str">
+        <v/>
+      </c>
+      <c r="J1055" t="str">
+        <v/>
+      </c>
+      <c r="K1055" t="str">
+        <v/>
+      </c>
+      <c r="L1055" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1056">
+      <c r="A1056" t="str">
+        <v/>
+      </c>
+      <c r="B1056" t="str">
+        <v>삼성웰스토리축구단</v>
+      </c>
+      <c r="C1056" t="str">
+        <v>화성시 병점구</v>
+      </c>
+      <c r="D1056" t="str">
+        <v>경기도 화성시 병점구 삼성전자로 1</v>
+      </c>
+      <c r="E1056" t="str">
+        <v>37.223466</v>
+      </c>
+      <c r="F1056" t="str">
+        <v>127.063346</v>
+      </c>
+      <c r="G1056" t="str">
+        <v/>
+      </c>
+      <c r="H1056" t="str">
+        <v/>
+      </c>
+      <c r="I1056" t="str">
+        <v/>
+      </c>
+      <c r="J1056" t="str">
+        <v/>
+      </c>
+      <c r="K1056" t="str">
+        <v/>
+      </c>
+      <c r="L1056" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1057">
+      <c r="A1057" t="str">
+        <v/>
+      </c>
+      <c r="B1057" t="str">
+        <v>장금이한식뷔페</v>
+      </c>
+      <c r="C1057" t="str">
+        <v>용인시 기흥구</v>
+      </c>
+      <c r="D1057" t="str">
+        <v>경기도 용인시 기흥구 서천로201번길 11</v>
+      </c>
+      <c r="E1057" t="str">
+        <v>37.231426</v>
+      </c>
+      <c r="F1057" t="str">
+        <v>127.071894</v>
+      </c>
+      <c r="G1057" t="str">
+        <v/>
+      </c>
+      <c r="H1057" t="str">
+        <v/>
+      </c>
+      <c r="I1057" t="str">
+        <v/>
+      </c>
+      <c r="J1057" t="str">
+        <v/>
+      </c>
+      <c r="K1057" t="str">
+        <v/>
+      </c>
+      <c r="L1057" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1058">
+      <c r="A1058" t="str">
+        <v/>
+      </c>
+      <c r="B1058" t="str">
+        <v>파주경찰서복지회</v>
+      </c>
+      <c r="C1058" t="str">
+        <v>파주시</v>
+      </c>
+      <c r="D1058" t="str">
+        <v>경기도 파주시 쇠재로 140</v>
+      </c>
+      <c r="E1058" t="str">
+        <v>37.753707</v>
+      </c>
+      <c r="F1058" t="str">
+        <v>126.778770</v>
+      </c>
+      <c r="G1058" t="str">
+        <v/>
+      </c>
+      <c r="H1058" t="str">
+        <v/>
+      </c>
+      <c r="I1058" t="str">
+        <v/>
+      </c>
+      <c r="J1058" t="str">
+        <v/>
+      </c>
+      <c r="K1058" t="str">
+        <v/>
+      </c>
+      <c r="L1058" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1059">
+      <c r="A1059" t="str">
+        <v/>
+      </c>
+      <c r="B1059" t="str">
+        <v>제이앤제이</v>
+      </c>
+      <c r="C1059" t="str">
+        <v>파주시</v>
+      </c>
+      <c r="D1059" t="str">
+        <v>경기도 파주시 금릉역로 62</v>
+      </c>
+      <c r="E1059" t="str">
+        <v>37.750469</v>
+      </c>
+      <c r="F1059" t="str">
+        <v>126.767172</v>
+      </c>
+      <c r="G1059" t="str">
+        <v/>
+      </c>
+      <c r="H1059" t="str">
+        <v/>
+      </c>
+      <c r="I1059" t="str">
+        <v/>
+      </c>
+      <c r="J1059" t="str">
+        <v/>
+      </c>
+      <c r="K1059" t="str">
+        <v/>
+      </c>
+      <c r="L1059" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1060">
+      <c r="A1060" t="str">
+        <v/>
+      </c>
+      <c r="B1060" t="str">
+        <v>피제이푸드</v>
+      </c>
+      <c r="C1060" t="str">
+        <v>파주시</v>
+      </c>
+      <c r="D1060" t="str">
+        <v>경기도 파주시 한마음2길 35</v>
+      </c>
+      <c r="E1060" t="str">
+        <v>37.756920</v>
+      </c>
+      <c r="F1060" t="str">
+        <v>126.772201</v>
+      </c>
+      <c r="G1060" t="str">
+        <v/>
+      </c>
+      <c r="H1060" t="str">
+        <v/>
+      </c>
+      <c r="I1060" t="str">
+        <v/>
+      </c>
+      <c r="J1060" t="str">
+        <v/>
+      </c>
+      <c r="K1060" t="str">
+        <v/>
+      </c>
+      <c r="L1060" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1061">
+      <c r="A1061" t="str">
+        <v/>
+      </c>
+      <c r="B1061" t="str">
+        <v>자연빌리지</v>
+      </c>
+      <c r="C1061" t="str">
+        <v>파주시</v>
+      </c>
+      <c r="D1061" t="str">
+        <v>경기도 파주시 조리읍 능안로 334</v>
+      </c>
+      <c r="E1061" t="str">
+        <v>37.739806</v>
+      </c>
+      <c r="F1061" t="str">
+        <v>126.788999</v>
+      </c>
+      <c r="G1061" t="str">
+        <v/>
+      </c>
+      <c r="H1061" t="str">
+        <v/>
+      </c>
+      <c r="I1061" t="str">
+        <v/>
+      </c>
+      <c r="J1061" t="str">
+        <v/>
+      </c>
+      <c r="K1061" t="str">
+        <v/>
+      </c>
+      <c r="L1061" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1062">
+      <c r="A1062" t="str">
+        <v/>
+      </c>
+      <c r="B1062" t="str">
+        <v>명성에프에스</v>
+      </c>
+      <c r="C1062" t="str">
+        <v>파주시</v>
+      </c>
+      <c r="D1062" t="str">
+        <v>경기도 파주시 중앙로 279</v>
+      </c>
+      <c r="E1062" t="str">
+        <v>37.760821</v>
+      </c>
+      <c r="F1062" t="str">
+        <v>126.776604</v>
+      </c>
+      <c r="G1062" t="str">
+        <v/>
+      </c>
+      <c r="H1062" t="str">
+        <v/>
+      </c>
+      <c r="I1062" t="str">
+        <v/>
+      </c>
+      <c r="J1062" t="str">
+        <v/>
+      </c>
+      <c r="K1062" t="str">
+        <v/>
+      </c>
+      <c r="L1062" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1063">
+      <c r="A1063" t="str">
+        <v/>
+      </c>
+      <c r="B1063" t="str">
+        <v>업소명없음</v>
+      </c>
+      <c r="C1063" t="str">
+        <v>파주시</v>
+      </c>
+      <c r="D1063" t="str">
+        <v>경기도 파주시 문화로 56</v>
+      </c>
+      <c r="E1063" t="str">
+        <v>37.759461</v>
+      </c>
+      <c r="F1063" t="str">
+        <v>126.776721</v>
+      </c>
+      <c r="G1063" t="str">
+        <v/>
+      </c>
+      <c r="H1063" t="str">
+        <v/>
+      </c>
+      <c r="I1063" t="str">
+        <v/>
+      </c>
+      <c r="J1063" t="str">
+        <v/>
+      </c>
+      <c r="K1063" t="str">
+        <v/>
+      </c>
+      <c r="L1063" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1064">
+      <c r="A1064" t="str">
+        <v/>
+      </c>
+      <c r="B1064" t="str">
+        <v>섬김푸드시스템</v>
+      </c>
+      <c r="C1064" t="str">
+        <v>파주시</v>
+      </c>
+      <c r="D1064" t="str">
+        <v>경기도 파주시 하지석길 355</v>
+      </c>
+      <c r="E1064" t="str">
+        <v>37.756390</v>
+      </c>
+      <c r="F1064" t="str">
+        <v>126.750415</v>
+      </c>
+      <c r="G1064" t="str">
+        <v/>
+      </c>
+      <c r="H1064" t="str">
+        <v/>
+      </c>
+      <c r="I1064" t="str">
+        <v/>
+      </c>
+      <c r="J1064" t="str">
+        <v/>
+      </c>
+      <c r="K1064" t="str">
+        <v/>
+      </c>
+      <c r="L1064" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1065">
+      <c r="A1065" t="str">
+        <v/>
+      </c>
+      <c r="B1065" t="str">
+        <v>주현</v>
+      </c>
+      <c r="C1065" t="str">
+        <v>파주시</v>
+      </c>
+      <c r="D1065" t="str">
+        <v>경기도 파주시 중앙로 280</v>
+      </c>
+      <c r="E1065" t="str">
+        <v>37.761047</v>
+      </c>
+      <c r="F1065" t="str">
+        <v>126.777091</v>
+      </c>
+      <c r="G1065" t="str">
+        <v/>
+      </c>
+      <c r="H1065" t="str">
+        <v/>
+      </c>
+      <c r="I1065" t="str">
+        <v/>
+      </c>
+      <c r="J1065" t="str">
+        <v/>
+      </c>
+      <c r="K1065" t="str">
+        <v/>
+      </c>
+      <c r="L1065" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1066">
+      <c r="A1066" t="str">
+        <v/>
+      </c>
+      <c r="B1066" t="str">
+        <v>금촌한식부페</v>
+      </c>
+      <c r="C1066" t="str">
+        <v>파주시</v>
+      </c>
+      <c r="D1066" t="str">
+        <v>경기도 파주시 금정6길 32-7</v>
+      </c>
+      <c r="E1066" t="str">
+        <v>37.758058</v>
+      </c>
+      <c r="F1066" t="str">
+        <v>126.778144</v>
+      </c>
+      <c r="G1066" t="str">
+        <v/>
+      </c>
+      <c r="H1066" t="str">
+        <v/>
+      </c>
+      <c r="I1066" t="str">
+        <v/>
+      </c>
+      <c r="J1066" t="str">
+        <v/>
+      </c>
+      <c r="K1066" t="str">
+        <v/>
+      </c>
+      <c r="L1066" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1067">
+      <c r="A1067" t="str">
+        <v/>
+      </c>
+      <c r="B1067" t="str">
+        <v>제일한식부페</v>
+      </c>
+      <c r="C1067" t="str">
+        <v>파주시</v>
+      </c>
+      <c r="D1067" t="str">
+        <v>경기도 파주시 월롱산로 61-9</v>
+      </c>
+      <c r="E1067" t="str">
+        <v>37.780752</v>
+      </c>
+      <c r="F1067" t="str">
+        <v>126.763819</v>
+      </c>
+      <c r="G1067" t="str">
+        <v/>
+      </c>
+      <c r="H1067" t="str">
+        <v/>
+      </c>
+      <c r="I1067" t="str">
+        <v/>
+      </c>
+      <c r="J1067" t="str">
+        <v/>
+      </c>
+      <c r="K1067" t="str">
+        <v/>
+      </c>
+      <c r="L1067" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1068">
+      <c r="A1068" t="str">
+        <v/>
+      </c>
+      <c r="B1068" t="str">
+        <v>라이프푸드</v>
+      </c>
+      <c r="C1068" t="str">
+        <v>파주시</v>
+      </c>
+      <c r="D1068" t="str">
+        <v>경기도 파주시 조리읍 뇌조로 34-9</v>
+      </c>
+      <c r="E1068" t="str">
+        <v>37.751667</v>
+      </c>
+      <c r="F1068" t="str">
+        <v>126.807008</v>
+      </c>
+      <c r="G1068" t="str">
+        <v/>
+      </c>
+      <c r="H1068" t="str">
+        <v/>
+      </c>
+      <c r="I1068" t="str">
+        <v/>
+      </c>
+      <c r="J1068" t="str">
+        <v/>
+      </c>
+      <c r="K1068" t="str">
+        <v/>
+      </c>
+      <c r="L1068" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1069">
+      <c r="A1069" t="str">
+        <v/>
+      </c>
+      <c r="B1069" t="str">
+        <v>알라뷰한식뷔페</v>
+      </c>
+      <c r="C1069" t="str">
+        <v>파주시</v>
+      </c>
+      <c r="D1069" t="str">
+        <v>경기도 파주시 조리읍 능안로 322</v>
+      </c>
+      <c r="E1069" t="str">
+        <v>37.740425</v>
+      </c>
+      <c r="F1069" t="str">
+        <v>126.787602</v>
+      </c>
+      <c r="G1069" t="str">
+        <v/>
+      </c>
+      <c r="H1069" t="str">
+        <v/>
+      </c>
+      <c r="I1069" t="str">
+        <v/>
+      </c>
+      <c r="J1069" t="str">
+        <v/>
+      </c>
+      <c r="K1069" t="str">
+        <v/>
+      </c>
+      <c r="L1069" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1070">
+      <c r="A1070" t="str">
+        <v/>
+      </c>
+      <c r="B1070" t="str">
+        <v>복청한식뷔페</v>
+      </c>
+      <c r="C1070" t="str">
+        <v>파주시</v>
+      </c>
+      <c r="D1070" t="str">
+        <v>경기도 파주시 조리읍 능안로 150</v>
+      </c>
+      <c r="E1070" t="str">
+        <v>37.740496</v>
+      </c>
+      <c r="F1070" t="str">
+        <v>126.791607</v>
+      </c>
+      <c r="G1070" t="str">
+        <v/>
+      </c>
+      <c r="H1070" t="str">
+        <v/>
+      </c>
+      <c r="I1070" t="str">
+        <v/>
+      </c>
+      <c r="J1070" t="str">
+        <v/>
+      </c>
+      <c r="K1070" t="str">
+        <v/>
+      </c>
+      <c r="L1070" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1071">
+      <c r="A1071" t="str">
+        <v/>
+      </c>
+      <c r="B1071" t="str">
+        <v>아이엔지엘스</v>
+      </c>
+      <c r="C1071" t="str">
+        <v>이천시</v>
+      </c>
+      <c r="D1071" t="str">
+        <v>경기도 이천시 이섭대천로 1411</v>
+      </c>
+      <c r="E1071" t="str">
+        <v>37.293878</v>
+      </c>
+      <c r="F1071" t="str">
+        <v>127.455665</v>
+      </c>
+      <c r="G1071" t="str">
+        <v/>
+      </c>
+      <c r="H1071" t="str">
+        <v/>
+      </c>
+      <c r="I1071" t="str">
+        <v/>
+      </c>
+      <c r="J1071" t="str">
+        <v/>
+      </c>
+      <c r="K1071" t="str">
+        <v/>
+      </c>
+      <c r="L1071" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1072">
+      <c r="A1072" t="str">
+        <v/>
+      </c>
+      <c r="B1072" t="str">
+        <v>푸른푸드서비스</v>
+      </c>
+      <c r="C1072" t="str">
+        <v>이천시</v>
+      </c>
+      <c r="D1072" t="str">
+        <v>경기도 이천시 사음로 42-25</v>
+      </c>
+      <c r="E1072" t="str">
+        <v>37.298238</v>
+      </c>
+      <c r="F1072" t="str">
+        <v>127.419273</v>
+      </c>
+      <c r="G1072" t="str">
+        <v/>
+      </c>
+      <c r="H1072" t="str">
+        <v/>
+      </c>
+      <c r="I1072" t="str">
+        <v/>
+      </c>
+      <c r="J1072" t="str">
+        <v/>
+      </c>
+      <c r="K1072" t="str">
+        <v/>
+      </c>
+      <c r="L1072" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1073">
+      <c r="A1073" t="str">
+        <v/>
+      </c>
+      <c r="B1073" t="str">
+        <v>동원홈후드세람저축은행본사점</v>
+      </c>
+      <c r="C1073" t="str">
+        <v>이천시</v>
+      </c>
+      <c r="D1073" t="str">
+        <v>경기도 이천시 중리천로 50</v>
+      </c>
+      <c r="E1073" t="str">
+        <v>37.279932</v>
+      </c>
+      <c r="F1073" t="str">
+        <v>127.443268</v>
+      </c>
+      <c r="G1073" t="str">
+        <v/>
+      </c>
+      <c r="H1073" t="str">
+        <v/>
+      </c>
+      <c r="I1073" t="str">
+        <v/>
+      </c>
+      <c r="J1073" t="str">
+        <v/>
+      </c>
+      <c r="K1073" t="str">
+        <v/>
+      </c>
+      <c r="L1073" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1074">
+      <c r="A1074" t="str">
+        <v/>
+      </c>
+      <c r="B1074" t="str">
+        <v>스카이부페</v>
+      </c>
+      <c r="C1074" t="str">
+        <v>이천시</v>
+      </c>
+      <c r="D1074" t="str">
+        <v>경기도 이천시 중리천로 98</v>
+      </c>
+      <c r="E1074" t="str">
+        <v>37.277563</v>
+      </c>
+      <c r="F1074" t="str">
+        <v>127.447809</v>
+      </c>
+      <c r="G1074" t="str">
+        <v/>
+      </c>
+      <c r="H1074" t="str">
+        <v/>
+      </c>
+      <c r="I1074" t="str">
+        <v/>
+      </c>
+      <c r="J1074" t="str">
+        <v/>
+      </c>
+      <c r="K1074" t="str">
+        <v/>
+      </c>
+      <c r="L1074" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1075">
+      <c r="A1075" t="str">
+        <v/>
+      </c>
+      <c r="B1075" t="str">
+        <v>은혜부페</v>
+      </c>
+      <c r="C1075" t="str">
+        <v>이천시</v>
+      </c>
+      <c r="D1075" t="str">
+        <v>경기도 이천시 설봉로58번길 18</v>
+      </c>
+      <c r="E1075" t="str">
+        <v>37.281199</v>
+      </c>
+      <c r="F1075" t="str">
+        <v>127.439306</v>
+      </c>
+      <c r="G1075" t="str">
+        <v/>
+      </c>
+      <c r="H1075" t="str">
+        <v/>
+      </c>
+      <c r="I1075" t="str">
+        <v/>
+      </c>
+      <c r="J1075" t="str">
+        <v/>
+      </c>
+      <c r="K1075" t="str">
+        <v/>
+      </c>
+      <c r="L1075" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1076">
+      <c r="A1076" t="str">
+        <v/>
+      </c>
+      <c r="B1076" t="str">
+        <v>구만리대박한식부페</v>
+      </c>
+      <c r="C1076" t="str">
+        <v>이천시</v>
+      </c>
+      <c r="D1076" t="str">
+        <v>경기도 이천시 구만리로 229</v>
+      </c>
+      <c r="E1076" t="str">
+        <v>37.276101</v>
+      </c>
+      <c r="F1076" t="str">
+        <v>127.457869</v>
+      </c>
+      <c r="G1076" t="str">
+        <v/>
+      </c>
+      <c r="H1076" t="str">
+        <v/>
+      </c>
+      <c r="I1076" t="str">
+        <v/>
+      </c>
+      <c r="J1076" t="str">
+        <v/>
+      </c>
+      <c r="K1076" t="str">
+        <v/>
+      </c>
+      <c r="L1076" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1077">
+      <c r="A1077" t="str">
+        <v/>
+      </c>
+      <c r="B1077" t="str">
+        <v>동원홈푸드인그리디언이천점주</v>
+      </c>
+      <c r="C1077" t="str">
+        <v>이천시</v>
+      </c>
+      <c r="D1077" t="str">
+        <v>경기도 이천시 부발읍 중부대로 1346</v>
+      </c>
+      <c r="E1077" t="str">
+        <v>37.270686</v>
+      </c>
+      <c r="F1077" t="str">
+        <v>127.466969</v>
+      </c>
+      <c r="G1077" t="str">
+        <v/>
+      </c>
+      <c r="H1077" t="str">
+        <v/>
+      </c>
+      <c r="I1077" t="str">
+        <v/>
+      </c>
+      <c r="J1077" t="str">
+        <v/>
+      </c>
+      <c r="K1077" t="str">
+        <v/>
+      </c>
+      <c r="L1077" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1078">
+      <c r="A1078" t="str">
+        <v/>
+      </c>
+      <c r="B1078" t="str">
+        <v>다도한식부페</v>
+      </c>
+      <c r="C1078" t="str">
+        <v>이천시</v>
+      </c>
+      <c r="D1078" t="str">
+        <v>경기도 이천시 부악로 8</v>
+      </c>
+      <c r="E1078" t="str">
+        <v>37.275922</v>
+      </c>
+      <c r="F1078" t="str">
+        <v>127.436197</v>
+      </c>
+      <c r="G1078" t="str">
+        <v/>
+      </c>
+      <c r="H1078" t="str">
+        <v/>
+      </c>
+      <c r="I1078" t="str">
+        <v/>
+      </c>
+      <c r="J1078" t="str">
+        <v/>
+      </c>
+      <c r="K1078" t="str">
+        <v/>
+      </c>
+      <c r="L1078" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1079">
+      <c r="A1079" t="str">
+        <v/>
+      </c>
+      <c r="B1079" t="str">
+        <v>구만리대박한식부페</v>
+      </c>
+      <c r="C1079" t="str">
+        <v>이천시</v>
+      </c>
+      <c r="D1079" t="str">
+        <v>경기도 이천시 구만리로 229</v>
+      </c>
+      <c r="E1079" t="str">
+        <v>37.276101</v>
+      </c>
+      <c r="F1079" t="str">
+        <v>127.457869</v>
+      </c>
+      <c r="G1079" t="str">
+        <v/>
+      </c>
+      <c r="H1079" t="str">
+        <v/>
+      </c>
+      <c r="I1079" t="str">
+        <v/>
+      </c>
+      <c r="J1079" t="str">
+        <v/>
+      </c>
+      <c r="K1079" t="str">
+        <v/>
+      </c>
+      <c r="L1079" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1080">
+      <c r="A1080" t="str">
+        <v/>
+      </c>
+      <c r="B1080" t="str">
+        <v>7080열린공간</v>
+      </c>
+      <c r="C1080" t="str">
+        <v>이천시</v>
+      </c>
+      <c r="D1080" t="str">
+        <v>경기도 이천시 어재연로 42-1</v>
+      </c>
+      <c r="E1080" t="str">
+        <v>37.279976</v>
+      </c>
+      <c r="F1080" t="str">
+        <v>127.445929</v>
+      </c>
+      <c r="G1080" t="str">
+        <v/>
+      </c>
+      <c r="H1080" t="str">
+        <v/>
+      </c>
+      <c r="I1080" t="str">
+        <v/>
+      </c>
+      <c r="J1080" t="str">
+        <v/>
+      </c>
+      <c r="K1080" t="str">
+        <v/>
+      </c>
+      <c r="L1080" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1081">
+      <c r="A1081" t="str">
+        <v/>
+      </c>
+      <c r="B1081" t="str">
+        <v>사음동한식부페</v>
+      </c>
+      <c r="C1081" t="str">
+        <v>이천시</v>
+      </c>
+      <c r="D1081" t="str">
+        <v>경기도 이천시 경충대로 2954</v>
+      </c>
+      <c r="E1081" t="str">
+        <v>37.295086</v>
+      </c>
+      <c r="F1081" t="str">
+        <v>127.416425</v>
+      </c>
+      <c r="G1081" t="str">
+        <v/>
+      </c>
+      <c r="H1081" t="str">
+        <v/>
+      </c>
+      <c r="I1081" t="str">
+        <v/>
+      </c>
+      <c r="J1081" t="str">
+        <v/>
+      </c>
+      <c r="K1081" t="str">
+        <v/>
+      </c>
+      <c r="L1081" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1082">
+      <c r="A1082" t="str">
+        <v/>
+      </c>
+      <c r="B1082" t="str">
+        <v>쿠우쿠우</v>
+      </c>
+      <c r="C1082" t="str">
+        <v>이천시</v>
+      </c>
+      <c r="D1082" t="str">
+        <v>경기도 이천시 중리천로 76</v>
+      </c>
+      <c r="E1082" t="str">
+        <v>37.278608</v>
+      </c>
+      <c r="F1082" t="str">
+        <v>127.445639</v>
+      </c>
+      <c r="G1082" t="str">
+        <v/>
+      </c>
+      <c r="H1082" t="str">
+        <v/>
+      </c>
+      <c r="I1082" t="str">
+        <v/>
+      </c>
+      <c r="J1082" t="str">
+        <v/>
+      </c>
+      <c r="K1082" t="str">
+        <v/>
+      </c>
+      <c r="L1082" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1083">
+      <c r="A1083" t="str">
+        <v/>
+      </c>
+      <c r="B1083" t="str">
+        <v>금강한식부페</v>
+      </c>
+      <c r="C1083" t="str">
+        <v>이천시</v>
+      </c>
+      <c r="D1083" t="str">
+        <v>경기도 이천시 애련정로 57</v>
+      </c>
+      <c r="E1083" t="str">
+        <v>37.277290</v>
+      </c>
+      <c r="F1083" t="str">
+        <v>127.453400</v>
+      </c>
+      <c r="G1083" t="str">
+        <v/>
+      </c>
+      <c r="H1083" t="str">
+        <v/>
+      </c>
+      <c r="I1083" t="str">
+        <v/>
+      </c>
+      <c r="J1083" t="str">
+        <v/>
+      </c>
+      <c r="K1083" t="str">
+        <v/>
+      </c>
+      <c r="L1083" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1084">
+      <c r="A1084" t="str">
+        <v/>
+      </c>
+      <c r="B1084" t="str">
+        <v>이천시청구내식당</v>
+      </c>
+      <c r="C1084" t="str">
+        <v>이천시</v>
+      </c>
+      <c r="D1084" t="str">
+        <v>경기도 이천시 부악로 40</v>
+      </c>
+      <c r="E1084" t="str">
+        <v>37.272124</v>
+      </c>
+      <c r="F1084" t="str">
+        <v>127.435037</v>
+      </c>
+      <c r="G1084" t="str">
+        <v/>
+      </c>
+      <c r="H1084" t="str">
+        <v/>
+      </c>
+      <c r="I1084" t="str">
+        <v/>
+      </c>
+      <c r="J1084" t="str">
+        <v/>
+      </c>
+      <c r="K1084" t="str">
+        <v/>
+      </c>
+      <c r="L1084" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1085">
+      <c r="A1085" t="str">
+        <v/>
+      </c>
+      <c r="B1085" t="str">
+        <v>엘케이엠</v>
+      </c>
+      <c r="C1085" t="str">
+        <v>이천시</v>
+      </c>
+      <c r="D1085" t="str">
+        <v>경기도 이천시 애련정로 57</v>
+      </c>
+      <c r="E1085" t="str">
+        <v>37.277200</v>
+      </c>
+      <c r="F1085" t="str">
+        <v>127.453298</v>
+      </c>
+      <c r="G1085" t="str">
+        <v/>
+      </c>
+      <c r="H1085" t="str">
+        <v/>
+      </c>
+      <c r="I1085" t="str">
+        <v/>
+      </c>
+      <c r="J1085" t="str">
+        <v/>
+      </c>
+      <c r="K1085" t="str">
+        <v/>
+      </c>
+      <c r="L1085" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1086">
+      <c r="A1086" t="str">
+        <v/>
+      </c>
+      <c r="B1086" t="str">
+        <v>푸드링</v>
+      </c>
+      <c r="C1086" t="str">
+        <v>이천시</v>
+      </c>
+      <c r="D1086" t="str">
+        <v>경기도 이천시 경충대로 2564</v>
+      </c>
+      <c r="E1086" t="str">
+        <v>37.275219</v>
+      </c>
+      <c r="F1086" t="str">
+        <v>127.448235</v>
+      </c>
+      <c r="G1086" t="str">
+        <v/>
+      </c>
+      <c r="H1086" t="str">
+        <v/>
+      </c>
+      <c r="I1086" t="str">
+        <v/>
+      </c>
+      <c r="J1086" t="str">
+        <v/>
+      </c>
+      <c r="K1086" t="str">
+        <v/>
+      </c>
+      <c r="L1086" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1087">
+      <c r="A1087" t="str">
+        <v/>
+      </c>
+      <c r="B1087" t="str">
+        <v>삼성웰스토리오비맥주이천공장</v>
+      </c>
+      <c r="C1087" t="str">
+        <v>이천시</v>
+      </c>
+      <c r="D1087" t="str">
+        <v>경기도 이천시 부발읍 경충대로 2314</v>
+      </c>
+      <c r="E1087" t="str">
+        <v>37.267797</v>
+      </c>
+      <c r="F1087" t="str">
+        <v>127.470818</v>
+      </c>
+      <c r="G1087" t="str">
+        <v/>
+      </c>
+      <c r="H1087" t="str">
+        <v/>
+      </c>
+      <c r="I1087" t="str">
+        <v/>
+      </c>
+      <c r="J1087" t="str">
+        <v/>
+      </c>
+      <c r="K1087" t="str">
+        <v/>
+      </c>
+      <c r="L1087" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1088">
+      <c r="A1088" t="str">
+        <v/>
+      </c>
+      <c r="B1088" t="str">
+        <v>그린식당남경구내식당</v>
+      </c>
+      <c r="C1088" t="str">
+        <v>평택시</v>
+      </c>
+      <c r="D1088" t="str">
+        <v>경기도 평택시 진위면 삼남로 745-41</v>
+      </c>
+      <c r="E1088" t="str">
+        <v>37.088255</v>
+      </c>
+      <c r="F1088" t="str">
+        <v>127.088552</v>
+      </c>
+      <c r="G1088" t="str">
+        <v/>
+      </c>
+      <c r="H1088" t="str">
+        <v/>
+      </c>
+      <c r="I1088" t="str">
+        <v/>
+      </c>
+      <c r="J1088" t="str">
+        <v/>
+      </c>
+      <c r="K1088" t="str">
+        <v/>
+      </c>
+      <c r="L1088" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1089">
+      <c r="A1089" t="str">
+        <v/>
+      </c>
+      <c r="B1089" t="str">
+        <v>그곳에가면</v>
+      </c>
+      <c r="C1089" t="str">
+        <v>평택시</v>
+      </c>
+      <c r="D1089" t="str">
+        <v>경기도 평택시 진위면 견산2길 1</v>
+      </c>
+      <c r="E1089" t="str">
+        <v>37.106075</v>
+      </c>
+      <c r="F1089" t="str">
+        <v>127.079696</v>
+      </c>
+      <c r="G1089" t="str">
+        <v/>
+      </c>
+      <c r="H1089" t="str">
+        <v/>
+      </c>
+      <c r="I1089" t="str">
+        <v/>
+      </c>
+      <c r="J1089" t="str">
+        <v/>
+      </c>
+      <c r="K1089" t="str">
+        <v/>
+      </c>
+      <c r="L1089" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1090">
+      <c r="A1090" t="str">
+        <v/>
+      </c>
+      <c r="B1090" t="str">
+        <v>전주한식뷔페지산점</v>
+      </c>
+      <c r="C1090" t="str">
+        <v>평택시</v>
+      </c>
+      <c r="D1090" t="str">
+        <v>경기도 평택시 지산로 276-1</v>
+      </c>
+      <c r="E1090" t="str">
+        <v>37.076472</v>
+      </c>
+      <c r="F1090" t="str">
+        <v>127.083871</v>
+      </c>
+      <c r="G1090" t="str">
+        <v/>
+      </c>
+      <c r="H1090" t="str">
+        <v/>
+      </c>
+      <c r="I1090" t="str">
+        <v/>
+      </c>
+      <c r="J1090" t="str">
+        <v/>
+      </c>
+      <c r="K1090" t="str">
+        <v/>
+      </c>
+      <c r="L1090" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1091">
+      <c r="A1091" t="str">
+        <v/>
+      </c>
+      <c r="B1091" t="str">
+        <v>인텔리안테크놀러지스구내식당</v>
+      </c>
+      <c r="C1091" t="str">
+        <v>평택시</v>
+      </c>
+      <c r="D1091" t="str">
+        <v>경기도 평택시 진위면 진위산단로 18-7</v>
+      </c>
+      <c r="E1091" t="str">
+        <v>37.120823</v>
+      </c>
+      <c r="F1091" t="str">
+        <v>127.083841</v>
+      </c>
+      <c r="G1091" t="str">
+        <v/>
+      </c>
+      <c r="H1091" t="str">
+        <v/>
+      </c>
+      <c r="I1091" t="str">
+        <v/>
+      </c>
+      <c r="J1091" t="str">
+        <v/>
+      </c>
+      <c r="K1091" t="str">
+        <v/>
+      </c>
+      <c r="L1091" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1092">
+      <c r="A1092" t="str">
+        <v/>
+      </c>
+      <c r="B1092" t="str">
+        <v>큐브한식뷔페</v>
+      </c>
+      <c r="C1092" t="str">
+        <v>평택시</v>
+      </c>
+      <c r="D1092" t="str">
+        <v>경기도 평택시 진위면 진위2산단로 15-20</v>
+      </c>
+      <c r="E1092" t="str">
+        <v>37.121941</v>
+      </c>
+      <c r="F1092" t="str">
+        <v>127.067762</v>
+      </c>
+      <c r="G1092" t="str">
+        <v/>
+      </c>
+      <c r="H1092" t="str">
+        <v/>
+      </c>
+      <c r="I1092" t="str">
+        <v/>
+      </c>
+      <c r="J1092" t="str">
+        <v/>
+      </c>
+      <c r="K1092" t="str">
+        <v/>
+      </c>
+      <c r="L1092" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1093">
+      <c r="A1093" t="str">
+        <v/>
+      </c>
+      <c r="B1093" t="str">
+        <v>제일푸드</v>
+      </c>
+      <c r="C1093" t="str">
+        <v>평택시</v>
+      </c>
+      <c r="D1093" t="str">
+        <v>경기도 평택시 목천로 72-19</v>
+      </c>
+      <c r="E1093" t="str">
+        <v>37.090094</v>
+      </c>
+      <c r="F1093" t="str">
+        <v>127.057454</v>
+      </c>
+      <c r="G1093" t="str">
+        <v/>
+      </c>
+      <c r="H1093" t="str">
+        <v/>
+      </c>
+      <c r="I1093" t="str">
+        <v/>
+      </c>
+      <c r="J1093" t="str">
+        <v/>
+      </c>
+      <c r="K1093" t="str">
+        <v/>
+      </c>
+      <c r="L1093" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1094">
+      <c r="A1094" t="str">
+        <v/>
+      </c>
+      <c r="B1094" t="str">
+        <v>동원홈푸드양전자시스템</v>
+      </c>
+      <c r="C1094" t="str">
+        <v>평택시</v>
+      </c>
+      <c r="D1094" t="str">
+        <v>경기도 평택시 진위면 진위산단로 53-37</v>
+      </c>
+      <c r="E1094" t="str">
+        <v>37.122455</v>
+      </c>
+      <c r="F1094" t="str">
+        <v>127.081266</v>
+      </c>
+      <c r="G1094" t="str">
+        <v/>
+      </c>
+      <c r="H1094" t="str">
+        <v/>
+      </c>
+      <c r="I1094" t="str">
+        <v/>
+      </c>
+      <c r="J1094" t="str">
+        <v/>
+      </c>
+      <c r="K1094" t="str">
+        <v/>
+      </c>
+      <c r="L1094" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1095">
+      <c r="A1095" t="str">
+        <v/>
+      </c>
+      <c r="B1095" t="str">
+        <v>인텔리안테크놀로지스구내식당</v>
+      </c>
+      <c r="C1095" t="str">
+        <v>평택시</v>
+      </c>
+      <c r="D1095" t="str">
+        <v>경기도 평택시 진위면 마산11로 30</v>
+      </c>
+      <c r="E1095" t="str">
+        <v>37.082470</v>
+      </c>
+      <c r="F1095" t="str">
+        <v>127.099510</v>
+      </c>
+      <c r="G1095" t="str">
+        <v/>
+      </c>
+      <c r="H1095" t="str">
+        <v/>
+      </c>
+      <c r="I1095" t="str">
+        <v/>
+      </c>
+      <c r="J1095" t="str">
+        <v/>
+      </c>
+      <c r="K1095" t="str">
+        <v/>
+      </c>
+      <c r="L1095" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1096">
+      <c r="A1096" t="str">
+        <v/>
+      </c>
+      <c r="B1096" t="str">
+        <v>가장한식부페</v>
+      </c>
+      <c r="C1096" t="str">
+        <v>평택시</v>
+      </c>
+      <c r="D1096" t="str">
+        <v>경기도 평택시 진위면 진위서로 84</v>
+      </c>
+      <c r="E1096" t="str">
+        <v>37.107485</v>
+      </c>
+      <c r="F1096" t="str">
+        <v>127.072508</v>
+      </c>
+      <c r="G1096" t="str">
+        <v/>
+      </c>
+      <c r="H1096" t="str">
+        <v/>
+      </c>
+      <c r="I1096" t="str">
+        <v/>
+      </c>
+      <c r="J1096" t="str">
+        <v/>
+      </c>
+      <c r="K1096" t="str">
+        <v/>
+      </c>
+      <c r="L1096" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1097">
+      <c r="A1097" t="str">
+        <v/>
+      </c>
+      <c r="B1097" t="str">
+        <v>바쎈구내식당</v>
+      </c>
+      <c r="C1097" t="str">
+        <v>평택시</v>
+      </c>
+      <c r="D1097" t="str">
+        <v>경기도 평택시 진위면 서탄로 50</v>
+      </c>
+      <c r="E1097" t="str">
+        <v>37.104186</v>
+      </c>
+      <c r="F1097" t="str">
+        <v>127.057937</v>
+      </c>
+      <c r="G1097" t="str">
+        <v/>
+      </c>
+      <c r="H1097" t="str">
+        <v/>
+      </c>
+      <c r="I1097" t="str">
+        <v/>
+      </c>
+      <c r="J1097" t="str">
+        <v/>
+      </c>
+      <c r="K1097" t="str">
+        <v/>
+      </c>
+      <c r="L1097" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1098">
+      <c r="A1098" t="str">
+        <v/>
+      </c>
+      <c r="B1098" t="str">
+        <v>수다한식뷔페</v>
+      </c>
+      <c r="C1098" t="str">
+        <v>평택시</v>
+      </c>
+      <c r="D1098" t="str">
+        <v>경기도 평택시 지산로 7-1</v>
+      </c>
+      <c r="E1098" t="str">
+        <v>37.079327</v>
+      </c>
+      <c r="F1098" t="str">
+        <v>127.055792</v>
+      </c>
+      <c r="G1098" t="str">
+        <v/>
+      </c>
+      <c r="H1098" t="str">
+        <v/>
+      </c>
+      <c r="I1098" t="str">
+        <v/>
+      </c>
+      <c r="J1098" t="str">
+        <v/>
+      </c>
+      <c r="K1098" t="str">
+        <v/>
+      </c>
+      <c r="L1098" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1099">
+      <c r="A1099" t="str">
+        <v/>
+      </c>
+      <c r="B1099" t="str">
+        <v>다온한식뷔페</v>
+      </c>
+      <c r="C1099" t="str">
+        <v>평택시</v>
+      </c>
+      <c r="D1099" t="str">
+        <v>경기도 평택시 진위면 진위2산단로 140</v>
+      </c>
+      <c r="E1099" t="str">
+        <v>37.119187</v>
+      </c>
+      <c r="F1099" t="str">
+        <v>127.077943</v>
+      </c>
+      <c r="G1099" t="str">
+        <v/>
+      </c>
+      <c r="H1099" t="str">
+        <v/>
+      </c>
+      <c r="I1099" t="str">
+        <v/>
+      </c>
+      <c r="J1099" t="str">
+        <v/>
+      </c>
+      <c r="K1099" t="str">
+        <v/>
+      </c>
+      <c r="L1099" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1100">
+      <c r="A1100" t="str">
+        <v/>
+      </c>
+      <c r="B1100" t="str">
+        <v>봉푸드</v>
+      </c>
+      <c r="C1100" t="str">
+        <v>평택시</v>
+      </c>
+      <c r="D1100" t="str">
+        <v>경기도 평택시 진위면 갈곶길 25-18</v>
+      </c>
+      <c r="E1100" t="str">
+        <v>37.120992</v>
+      </c>
+      <c r="F1100" t="str">
+        <v>127.072746</v>
+      </c>
+      <c r="G1100" t="str">
+        <v/>
+      </c>
+      <c r="H1100" t="str">
+        <v/>
+      </c>
+      <c r="I1100" t="str">
+        <v/>
+      </c>
+      <c r="J1100" t="str">
+        <v/>
+      </c>
+      <c r="K1100" t="str">
+        <v/>
+      </c>
+      <c r="L1100" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1101">
+      <c r="A1101" t="str">
+        <v/>
+      </c>
+      <c r="B1101" t="str">
+        <v>월드유통평택진위지점</v>
+      </c>
+      <c r="C1101" t="str">
+        <v>평택시</v>
+      </c>
+      <c r="D1101" t="str">
+        <v>경기도 평택시 진위면 진위2산단로 150</v>
+      </c>
+      <c r="E1101" t="str">
+        <v>37.117574</v>
+      </c>
+      <c r="F1101" t="str">
+        <v>127.077334</v>
+      </c>
+      <c r="G1101" t="str">
+        <v/>
+      </c>
+      <c r="H1101" t="str">
+        <v/>
+      </c>
+      <c r="I1101" t="str">
+        <v/>
+      </c>
+      <c r="J1101" t="str">
+        <v/>
+      </c>
+      <c r="K1101" t="str">
+        <v/>
+      </c>
+      <c r="L1101" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1102">
+      <c r="A1102" t="str">
+        <v/>
+      </c>
+      <c r="B1102" t="str">
+        <v>업소명없음</v>
+      </c>
+      <c r="C1102" t="str">
+        <v>평택시</v>
+      </c>
+      <c r="D1102" t="str">
+        <v>경기도 평택시 서탄면 서탄로 140</v>
+      </c>
+      <c r="E1102" t="str">
+        <v>37.105651</v>
+      </c>
+      <c r="F1102" t="str">
+        <v>127.047554</v>
+      </c>
+      <c r="G1102" t="str">
+        <v/>
+      </c>
+      <c r="H1102" t="str">
+        <v/>
+      </c>
+      <c r="I1102" t="str">
+        <v/>
+      </c>
+      <c r="J1102" t="str">
+        <v/>
+      </c>
+      <c r="K1102" t="str">
+        <v/>
+      </c>
+      <c r="L1102" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1103">
+      <c r="A1103" t="str">
+        <v/>
+      </c>
+      <c r="B1103" t="str">
+        <v>고메드갤러리아평택물류센터직원식당</v>
+      </c>
+      <c r="C1103" t="str">
+        <v>평택시</v>
+      </c>
+      <c r="D1103" t="str">
+        <v>경기도 평택시 진위면 마산8로 10</v>
+      </c>
+      <c r="E1103" t="str">
+        <v>37.087201</v>
+      </c>
+      <c r="F1103" t="str">
+        <v>127.099123</v>
+      </c>
+      <c r="G1103" t="str">
+        <v/>
+      </c>
+      <c r="H1103" t="str">
+        <v/>
+      </c>
+      <c r="I1103" t="str">
+        <v/>
+      </c>
+      <c r="J1103" t="str">
+        <v/>
+      </c>
+      <c r="K1103" t="str">
+        <v/>
+      </c>
+      <c r="L1103" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1104">
+      <c r="A1104" t="str">
+        <v/>
+      </c>
+      <c r="B1104" t="str">
+        <v>진위행복뷔페</v>
+      </c>
+      <c r="C1104" t="str">
+        <v>평택시</v>
+      </c>
+      <c r="D1104" t="str">
+        <v>경기도 평택시 진위면 진위서로 48</v>
+      </c>
+      <c r="E1104" t="str">
+        <v>37.108398</v>
+      </c>
+      <c r="F1104" t="str">
+        <v>127.068167</v>
+      </c>
+      <c r="G1104" t="str">
+        <v/>
+      </c>
+      <c r="H1104" t="str">
+        <v/>
+      </c>
+      <c r="I1104" t="str">
+        <v/>
+      </c>
+      <c r="J1104" t="str">
+        <v/>
+      </c>
+      <c r="K1104" t="str">
+        <v/>
+      </c>
+      <c r="L1104" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1105">
+      <c r="A1105" t="str">
+        <v/>
+      </c>
+      <c r="B1105" t="str">
+        <v>선우푸드한식뷔페</v>
+      </c>
+      <c r="C1105" t="str">
+        <v>평택시</v>
+      </c>
+      <c r="D1105" t="str">
+        <v>경기도 평택시 특구로 54</v>
+      </c>
+      <c r="E1105" t="str">
+        <v>37.070384</v>
+      </c>
+      <c r="F1105" t="str">
+        <v>127.063837</v>
+      </c>
+      <c r="G1105" t="str">
+        <v/>
+      </c>
+      <c r="H1105" t="str">
+        <v/>
+      </c>
+      <c r="I1105" t="str">
+        <v/>
+      </c>
+      <c r="J1105" t="str">
+        <v/>
+      </c>
+      <c r="K1105" t="str">
+        <v/>
+      </c>
+      <c r="L1105" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1106">
+      <c r="A1106" t="str">
+        <v/>
+      </c>
+      <c r="B1106" t="str">
+        <v>쿠우쿠우송탄점</v>
+      </c>
+      <c r="C1106" t="str">
+        <v>평택시</v>
+      </c>
+      <c r="D1106" t="str">
+        <v>경기도 평택시 경기대로 1407</v>
+      </c>
+      <c r="E1106" t="str">
+        <v>37.070745</v>
+      </c>
+      <c r="F1106" t="str">
+        <v>127.064085</v>
+      </c>
+      <c r="G1106" t="str">
+        <v/>
+      </c>
+      <c r="H1106" t="str">
+        <v/>
+      </c>
+      <c r="I1106" t="str">
+        <v/>
+      </c>
+      <c r="J1106" t="str">
+        <v/>
+      </c>
+      <c r="K1106" t="str">
+        <v/>
+      </c>
+      <c r="L1106" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1107">
+      <c r="A1107" t="str">
+        <v/>
+      </c>
+      <c r="B1107" t="str">
+        <v>미가한식뷔페</v>
+      </c>
+      <c r="C1107" t="str">
+        <v>평택시</v>
+      </c>
+      <c r="D1107" t="str">
+        <v>경기도 평택시 진위면 가곡4길 9-36</v>
+      </c>
+      <c r="E1107" t="str">
+        <v>37.119761</v>
+      </c>
+      <c r="F1107" t="str">
+        <v>127.067310</v>
+      </c>
+      <c r="G1107" t="str">
+        <v/>
+      </c>
+      <c r="H1107" t="str">
+        <v/>
+      </c>
+      <c r="I1107" t="str">
+        <v/>
+      </c>
+      <c r="J1107" t="str">
+        <v/>
+      </c>
+      <c r="K1107" t="str">
+        <v/>
+      </c>
+      <c r="L1107" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1108">
+      <c r="A1108" t="str">
+        <v/>
+      </c>
+      <c r="B1108" t="str">
+        <v>구장한식부페</v>
+      </c>
+      <c r="C1108" t="str">
+        <v>화성시 만세구</v>
+      </c>
+      <c r="D1108" t="str">
+        <v>경기도 화성시 만세구 팔탄면 푸른들판로 617-11</v>
+      </c>
+      <c r="E1108" t="str">
+        <v>37.163679</v>
+      </c>
+      <c r="F1108" t="str">
+        <v>126.895711</v>
+      </c>
+      <c r="G1108" t="str">
+        <v/>
+      </c>
+      <c r="H1108" t="str">
+        <v/>
+      </c>
+      <c r="I1108" t="str">
+        <v/>
+      </c>
+      <c r="J1108" t="str">
+        <v/>
+      </c>
+      <c r="K1108" t="str">
+        <v/>
+      </c>
+      <c r="L1108" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1109">
+      <c r="A1109" t="str">
+        <v/>
+      </c>
+      <c r="B1109" t="str">
+        <v>늘푸른한식뷔페</v>
+      </c>
+      <c r="C1109" t="str">
+        <v>화성시 만세구</v>
+      </c>
+      <c r="D1109" t="str">
+        <v>경기도 화성시 만세구 팔탄면 푸른들판로 733</v>
+      </c>
+      <c r="E1109" t="str">
+        <v>37.172946</v>
+      </c>
+      <c r="F1109" t="str">
+        <v>126.890823</v>
+      </c>
+      <c r="G1109" t="str">
+        <v/>
+      </c>
+      <c r="H1109" t="str">
+        <v/>
+      </c>
+      <c r="I1109" t="str">
+        <v/>
+      </c>
+      <c r="J1109" t="str">
+        <v/>
+      </c>
+      <c r="K1109" t="str">
+        <v/>
+      </c>
+      <c r="L1109" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1110">
+      <c r="A1110" t="str">
+        <v/>
+      </c>
+      <c r="B1110" t="str">
+        <v>가본한식뷔페</v>
+      </c>
+      <c r="C1110" t="str">
+        <v>화성시 만세구</v>
+      </c>
+      <c r="D1110" t="str">
+        <v>경기도 화성시 만세구 팔탄면 시청로 1000</v>
+      </c>
+      <c r="E1110" t="str">
+        <v>37.169196</v>
+      </c>
+      <c r="F1110" t="str">
+        <v>126.898744</v>
+      </c>
+      <c r="G1110" t="str">
+        <v/>
+      </c>
+      <c r="H1110" t="str">
+        <v/>
+      </c>
+      <c r="I1110" t="str">
+        <v/>
+      </c>
+      <c r="J1110" t="str">
+        <v/>
+      </c>
+      <c r="K1110" t="str">
+        <v/>
+      </c>
+      <c r="L1110" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1111">
+      <c r="A1111" t="str">
+        <v/>
+      </c>
+      <c r="B1111" t="str">
+        <v>구장리맛집한식부페</v>
+      </c>
+      <c r="C1111" t="str">
+        <v>화성시 만세구</v>
+      </c>
+      <c r="D1111" t="str">
+        <v>경기도 화성시 만세구 팔탄면 푸른들판로 557-6</v>
+      </c>
+      <c r="E1111" t="str">
+        <v>37.158689</v>
+      </c>
+      <c r="F1111" t="str">
+        <v>126.898071</v>
+      </c>
+      <c r="G1111" t="str">
+        <v/>
+      </c>
+      <c r="H1111" t="str">
+        <v/>
+      </c>
+      <c r="I1111" t="str">
+        <v/>
+      </c>
+      <c r="J1111" t="str">
+        <v/>
+      </c>
+      <c r="K1111" t="str">
+        <v/>
+      </c>
+      <c r="L1111" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1112">
+      <c r="A1112" t="str">
+        <v/>
+      </c>
+      <c r="B1112" t="str">
+        <v>맛자랑한식부페</v>
+      </c>
+      <c r="C1112" t="str">
+        <v>화성시 만세구</v>
+      </c>
+      <c r="D1112" t="str">
+        <v>경기도 화성시 만세구 팔탄면 신양1길 89</v>
+      </c>
+      <c r="E1112" t="str">
+        <v>37.154461</v>
+      </c>
+      <c r="F1112" t="str">
+        <v>126.932524</v>
+      </c>
+      <c r="G1112" t="str">
+        <v/>
+      </c>
+      <c r="H1112" t="str">
+        <v/>
+      </c>
+      <c r="I1112" t="str">
+        <v/>
+      </c>
+      <c r="J1112" t="str">
+        <v/>
+      </c>
+      <c r="K1112" t="str">
+        <v/>
+      </c>
+      <c r="L1112" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1113">
+      <c r="A1113" t="str">
+        <v/>
+      </c>
+      <c r="B1113" t="str">
+        <v>채경이네구내식당</v>
+      </c>
+      <c r="C1113" t="str">
+        <v>화성시 효행구</v>
+      </c>
+      <c r="D1113" t="str">
+        <v>경기도 화성시 효행구 봉담읍 덕우공단1길 65-23</v>
+      </c>
+      <c r="E1113" t="str">
+        <v>37.160843</v>
+      </c>
+      <c r="F1113" t="str">
+        <v>126.921812</v>
+      </c>
+      <c r="G1113" t="str">
+        <v/>
+      </c>
+      <c r="H1113" t="str">
+        <v/>
+      </c>
+      <c r="I1113" t="str">
+        <v/>
+      </c>
+      <c r="J1113" t="str">
+        <v/>
+      </c>
+      <c r="K1113" t="str">
+        <v/>
+      </c>
+      <c r="L1113" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1114">
+      <c r="A1114" t="str">
+        <v/>
+      </c>
+      <c r="B1114" t="str">
+        <v>한샘한식뷔페</v>
+      </c>
+      <c r="C1114" t="str">
+        <v>화성시 만세구</v>
+      </c>
+      <c r="D1114" t="str">
+        <v>경기도 화성시 만세구 팔탄면 포승향남로 2960-85</v>
+      </c>
+      <c r="E1114" t="str">
+        <v>37.155412</v>
+      </c>
+      <c r="F1114" t="str">
+        <v>126.912732</v>
+      </c>
+      <c r="G1114" t="str">
+        <v/>
+      </c>
+      <c r="H1114" t="str">
+        <v/>
+      </c>
+      <c r="I1114" t="str">
+        <v/>
+      </c>
+      <c r="J1114" t="str">
+        <v/>
+      </c>
+      <c r="K1114" t="str">
+        <v/>
+      </c>
+      <c r="L1114" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1115">
+      <c r="A1115" t="str">
+        <v/>
+      </c>
+      <c r="B1115" t="str">
+        <v>예찬한식부페</v>
+      </c>
+      <c r="C1115" t="str">
+        <v>화성시 만세구</v>
+      </c>
+      <c r="D1115" t="str">
+        <v>경기도 화성시 만세구 팔탄면 푸른들판로 748</v>
+      </c>
+      <c r="E1115" t="str">
+        <v>37.174262</v>
+      </c>
+      <c r="F1115" t="str">
+        <v>126.891237</v>
+      </c>
+      <c r="G1115" t="str">
+        <v/>
+      </c>
+      <c r="H1115" t="str">
+        <v/>
+      </c>
+      <c r="I1115" t="str">
+        <v/>
+      </c>
+      <c r="J1115" t="str">
+        <v/>
+      </c>
+      <c r="K1115" t="str">
+        <v/>
+      </c>
+      <c r="L1115" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1116">
+      <c r="A1116" t="str">
+        <v/>
+      </c>
+      <c r="B1116" t="str">
+        <v>쓰리원파트너스</v>
+      </c>
+      <c r="C1116" t="str">
+        <v>화성시 효행구</v>
+      </c>
+      <c r="D1116" t="str">
+        <v>경기도 화성시 효행구 봉담읍 방골길 69</v>
+      </c>
+      <c r="E1116" t="str">
+        <v>37.163276</v>
+      </c>
+      <c r="F1116" t="str">
+        <v>126.938573</v>
+      </c>
+      <c r="G1116" t="str">
+        <v/>
+      </c>
+      <c r="H1116" t="str">
+        <v/>
+      </c>
+      <c r="I1116" t="str">
+        <v/>
+      </c>
+      <c r="J1116" t="str">
+        <v/>
+      </c>
+      <c r="K1116" t="str">
+        <v/>
+      </c>
+      <c r="L1116" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1117">
+      <c r="A1117" t="str">
+        <v/>
+      </c>
+      <c r="B1117" t="str">
+        <v>명품한식부페</v>
+      </c>
+      <c r="C1117" t="str">
+        <v>화성시 만세구</v>
+      </c>
+      <c r="D1117" t="str">
+        <v>경기도 화성시 만세구 팔탄면 푸른들판로 607</v>
+      </c>
+      <c r="E1117" t="str">
+        <v>37.162482</v>
+      </c>
+      <c r="F1117" t="str">
+        <v>126.896917</v>
+      </c>
+      <c r="G1117" t="str">
+        <v/>
+      </c>
+      <c r="H1117" t="str">
+        <v/>
+      </c>
+      <c r="I1117" t="str">
+        <v/>
+      </c>
+      <c r="J1117" t="str">
+        <v/>
+      </c>
+      <c r="K1117" t="str">
+        <v/>
+      </c>
+      <c r="L1117" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1118">
+      <c r="A1118" t="str">
+        <v/>
+      </c>
+      <c r="B1118" t="str">
+        <v>맛깔한식뷔페</v>
+      </c>
+      <c r="C1118" t="str">
+        <v>화성시 만세구</v>
+      </c>
+      <c r="D1118" t="str">
+        <v>경기도 화성시 만세구 팔탄면 푸른들판로 704</v>
+      </c>
+      <c r="E1118" t="str">
+        <v>37.170732</v>
+      </c>
+      <c r="F1118" t="str">
+        <v>126.892853</v>
+      </c>
+      <c r="G1118" t="str">
+        <v/>
+      </c>
+      <c r="H1118" t="str">
+        <v/>
+      </c>
+      <c r="I1118" t="str">
+        <v/>
+      </c>
+      <c r="J1118" t="str">
+        <v/>
+      </c>
+      <c r="K1118" t="str">
+        <v/>
+      </c>
+      <c r="L1118" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1119">
+      <c r="A1119" t="str">
+        <v/>
+      </c>
+      <c r="B1119" t="str">
+        <v>맛집한식뷔페</v>
+      </c>
+      <c r="C1119" t="str">
+        <v>화성시 효행구</v>
+      </c>
+      <c r="D1119" t="str">
+        <v>경기도 화성시 효행구 봉담읍 전원길 26</v>
+      </c>
+      <c r="E1119" t="str">
+        <v>37.178501</v>
+      </c>
+      <c r="F1119" t="str">
+        <v>126.933448</v>
+      </c>
+      <c r="G1119" t="str">
+        <v/>
+      </c>
+      <c r="H1119" t="str">
+        <v/>
+      </c>
+      <c r="I1119" t="str">
+        <v/>
+      </c>
+      <c r="J1119" t="str">
+        <v/>
+      </c>
+      <c r="K1119" t="str">
+        <v/>
+      </c>
+      <c r="L1119" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1120">
+      <c r="A1120" t="str">
+        <v/>
+      </c>
+      <c r="B1120" t="str">
+        <v>지연한식뷔페</v>
+      </c>
+      <c r="C1120" t="str">
+        <v>화성시 만세구</v>
+      </c>
+      <c r="D1120" t="str">
+        <v>경기도 화성시 만세구 팔탄면 시청로 1049</v>
+      </c>
+      <c r="E1120" t="str">
+        <v>37.172515</v>
+      </c>
+      <c r="F1120" t="str">
+        <v>126.902669</v>
+      </c>
+      <c r="G1120" t="str">
+        <v/>
+      </c>
+      <c r="H1120" t="str">
+        <v/>
+      </c>
+      <c r="I1120" t="str">
+        <v/>
+      </c>
+      <c r="J1120" t="str">
+        <v/>
+      </c>
+      <c r="K1120" t="str">
+        <v/>
+      </c>
+      <c r="L1120" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1121">
+      <c r="A1121" t="str">
+        <v/>
+      </c>
+      <c r="B1121" t="str">
+        <v>손맛한식부페</v>
+      </c>
+      <c r="C1121" t="str">
+        <v>화성시 효행구</v>
+      </c>
+      <c r="D1121" t="str">
+        <v>경기도 화성시 효행구 봉담읍 마당바위로 251</v>
+      </c>
+      <c r="E1121" t="str">
+        <v>37.165277</v>
+      </c>
+      <c r="F1121" t="str">
+        <v>126.923023</v>
+      </c>
+      <c r="G1121" t="str">
+        <v/>
+      </c>
+      <c r="H1121" t="str">
+        <v/>
+      </c>
+      <c r="I1121" t="str">
+        <v/>
+      </c>
+      <c r="J1121" t="str">
+        <v/>
+      </c>
+      <c r="K1121" t="str">
+        <v/>
+      </c>
+      <c r="L1121" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1122">
+      <c r="A1122" t="str">
+        <v/>
+      </c>
+      <c r="B1122" t="str">
+        <v>우리집한식뷔페</v>
+      </c>
+      <c r="C1122" t="str">
+        <v>화성시 효행구</v>
+      </c>
+      <c r="D1122" t="str">
+        <v>경기도 화성시 효행구 봉담읍 덕우공단2길 53</v>
+      </c>
+      <c r="E1122" t="str">
+        <v>37.155948</v>
+      </c>
+      <c r="F1122" t="str">
+        <v>126.918608</v>
+      </c>
+      <c r="G1122" t="str">
+        <v/>
+      </c>
+      <c r="H1122" t="str">
+        <v/>
+      </c>
+      <c r="I1122" t="str">
+        <v/>
+      </c>
+      <c r="J1122" t="str">
+        <v/>
+      </c>
+      <c r="K1122" t="str">
+        <v/>
+      </c>
+      <c r="L1122" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1123">
+      <c r="A1123" t="str">
+        <v/>
+      </c>
+      <c r="B1123" t="str">
+        <v>진흥구내식당</v>
+      </c>
+      <c r="C1123" t="str">
+        <v>화성시 만세구</v>
+      </c>
+      <c r="D1123" t="str">
+        <v>경기도 화성시 만세구 팔탄면 시청로 874-25</v>
+      </c>
+      <c r="E1123" t="str">
+        <v>37.167006</v>
+      </c>
+      <c r="F1123" t="str">
+        <v>126.887960</v>
+      </c>
+      <c r="G1123" t="str">
+        <v/>
+      </c>
+      <c r="H1123" t="str">
+        <v/>
+      </c>
+      <c r="I1123" t="str">
+        <v/>
+      </c>
+      <c r="J1123" t="str">
+        <v/>
+      </c>
+      <c r="K1123" t="str">
+        <v/>
+      </c>
+      <c r="L1123" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1124">
+      <c r="A1124" t="str">
+        <v/>
+      </c>
+      <c r="B1124" t="str">
+        <v>상록한식뷔페</v>
+      </c>
+      <c r="C1124" t="str">
+        <v>화성시 효행구</v>
+      </c>
+      <c r="D1124" t="str">
+        <v>경기도 화성시 효행구 봉담읍 갈담초교길 27-2</v>
+      </c>
+      <c r="E1124" t="str">
+        <v>37.174995</v>
+      </c>
+      <c r="F1124" t="str">
+        <v>126.931695</v>
+      </c>
+      <c r="G1124" t="str">
+        <v/>
+      </c>
+      <c r="H1124" t="str">
+        <v/>
+      </c>
+      <c r="I1124" t="str">
+        <v/>
+      </c>
+      <c r="J1124" t="str">
+        <v/>
+      </c>
+      <c r="K1124" t="str">
+        <v/>
+      </c>
+      <c r="L1124" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1125">
+      <c r="A1125" t="str">
+        <v/>
+      </c>
+      <c r="B1125" t="str">
+        <v>담소정한식뷔페</v>
+      </c>
+      <c r="C1125" t="str">
+        <v>화성시 효행구</v>
+      </c>
+      <c r="D1125" t="str">
+        <v>경기도 화성시 효행구 봉담읍 번던길 37-4</v>
+      </c>
+      <c r="E1125" t="str">
+        <v>37.177381</v>
+      </c>
+      <c r="F1125" t="str">
+        <v>126.944226</v>
+      </c>
+      <c r="G1125" t="str">
+        <v/>
+      </c>
+      <c r="H1125" t="str">
+        <v/>
+      </c>
+      <c r="I1125" t="str">
+        <v/>
+      </c>
+      <c r="J1125" t="str">
+        <v/>
+      </c>
+      <c r="K1125" t="str">
+        <v/>
+      </c>
+      <c r="L1125" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1126">
+      <c r="A1126" t="str">
+        <v/>
+      </c>
+      <c r="B1126" t="str">
+        <v>행운한식뷔페</v>
+      </c>
+      <c r="C1126" t="str">
+        <v>화성시 만세구</v>
+      </c>
+      <c r="D1126" t="str">
+        <v>경기도 화성시 만세구 팔탄면 푸른들판로 557-6</v>
+      </c>
+      <c r="E1126" t="str">
+        <v>37.158689</v>
+      </c>
+      <c r="F1126" t="str">
+        <v>126.898071</v>
+      </c>
+      <c r="G1126" t="str">
+        <v/>
+      </c>
+      <c r="H1126" t="str">
+        <v/>
+      </c>
+      <c r="I1126" t="str">
+        <v/>
+      </c>
+      <c r="J1126" t="str">
+        <v/>
+      </c>
+      <c r="K1126" t="str">
+        <v/>
+      </c>
+      <c r="L1126" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1127">
+      <c r="A1127" t="str">
+        <v/>
+      </c>
+      <c r="B1127" t="str">
+        <v>다드림한식뷔페</v>
+      </c>
+      <c r="C1127" t="str">
+        <v>화성시 효행구</v>
+      </c>
+      <c r="D1127" t="str">
+        <v>경기도 화성시 효행구 봉담읍 흰돌산길 39</v>
+      </c>
+      <c r="E1127" t="str">
+        <v>37.182142</v>
+      </c>
+      <c r="F1127" t="str">
+        <v>126.933704</v>
+      </c>
+      <c r="G1127" t="str">
+        <v/>
+      </c>
+      <c r="H1127" t="str">
+        <v/>
+      </c>
+      <c r="I1127" t="str">
+        <v/>
+      </c>
+      <c r="J1127" t="str">
+        <v/>
+      </c>
+      <c r="K1127" t="str">
+        <v/>
+      </c>
+      <c r="L1127" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1128">
+      <c r="A1128" t="str">
+        <v/>
+      </c>
+      <c r="B1128" t="str">
+        <v>다모아식당</v>
+      </c>
+      <c r="C1128" t="str">
+        <v>화성시 만세구</v>
+      </c>
+      <c r="D1128" t="str">
+        <v>경기도 화성시 만세구 팔탄면 푸른들판로 720-14</v>
+      </c>
+      <c r="E1128" t="str">
+        <v>37.172525</v>
+      </c>
+      <c r="F1128" t="str">
+        <v>126.893661</v>
+      </c>
+      <c r="G1128" t="str">
+        <v/>
+      </c>
+      <c r="H1128" t="str">
+        <v/>
+      </c>
+      <c r="I1128" t="str">
+        <v/>
+      </c>
+      <c r="J1128" t="str">
+        <v/>
+      </c>
+      <c r="K1128" t="str">
+        <v/>
+      </c>
+      <c r="L1128" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1129">
+      <c r="A1129" t="str">
+        <v/>
+      </c>
+      <c r="B1129" t="str">
+        <v>정든한식뷔페</v>
+      </c>
+      <c r="C1129" t="str">
+        <v>화성시 만세구</v>
+      </c>
+      <c r="D1129" t="str">
+        <v>경기도 화성시 만세구 팔탄면 시청로 933</v>
+      </c>
+      <c r="E1129" t="str">
+        <v>37.169569</v>
+      </c>
+      <c r="F1129" t="str">
+        <v>126.892978</v>
+      </c>
+      <c r="G1129" t="str">
+        <v/>
+      </c>
+      <c r="H1129" t="str">
+        <v/>
+      </c>
+      <c r="I1129" t="str">
+        <v/>
+      </c>
+      <c r="J1129" t="str">
+        <v/>
+      </c>
+      <c r="K1129" t="str">
+        <v/>
+      </c>
+      <c r="L1129" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1130">
+      <c r="A1130" t="str">
+        <v/>
+      </c>
+      <c r="B1130" t="str">
+        <v>화진한식뷔페</v>
+      </c>
+      <c r="C1130" t="str">
+        <v>화성시 만세구</v>
+      </c>
+      <c r="D1130" t="str">
+        <v>경기도 화성시 만세구 팔탄면 시청로 1204-2</v>
+      </c>
+      <c r="E1130" t="str">
+        <v>37.170549</v>
+      </c>
+      <c r="F1130" t="str">
+        <v>126.900408</v>
+      </c>
+      <c r="G1130" t="str">
+        <v/>
+      </c>
+      <c r="H1130" t="str">
+        <v/>
+      </c>
+      <c r="I1130" t="str">
+        <v/>
+      </c>
+      <c r="J1130" t="str">
+        <v/>
+      </c>
+      <c r="K1130" t="str">
+        <v/>
+      </c>
+      <c r="L1130" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1131">
+      <c r="A1131" t="str">
+        <v/>
+      </c>
+      <c r="B1131" t="str">
+        <v>아리랑한식뷔페</v>
+      </c>
+      <c r="C1131" t="str">
+        <v>화성시 효행구</v>
+      </c>
+      <c r="D1131" t="str">
+        <v>경기도 화성시 효행구 봉담읍 삼천병마로 817</v>
+      </c>
+      <c r="E1131" t="str">
+        <v>37.180729</v>
+      </c>
+      <c r="F1131" t="str">
+        <v>126.936881</v>
+      </c>
+      <c r="G1131" t="str">
+        <v/>
+      </c>
+      <c r="H1131" t="str">
+        <v/>
+      </c>
+      <c r="I1131" t="str">
+        <v/>
+      </c>
+      <c r="J1131" t="str">
+        <v/>
+      </c>
+      <c r="K1131" t="str">
+        <v/>
+      </c>
+      <c r="L1131" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1132">
+      <c r="A1132" t="str">
+        <v/>
+      </c>
+      <c r="B1132" t="str">
+        <v>은혜한식뷔페</v>
+      </c>
+      <c r="C1132" t="str">
+        <v>화성시 효행구</v>
+      </c>
+      <c r="D1132" t="str">
+        <v>경기도 화성시 효행구 봉담읍 흰돌산길 52</v>
+      </c>
+      <c r="E1132" t="str">
+        <v>37.183060</v>
+      </c>
+      <c r="F1132" t="str">
+        <v>126.932352</v>
+      </c>
+      <c r="G1132" t="str">
+        <v/>
+      </c>
+      <c r="H1132" t="str">
+        <v/>
+      </c>
+      <c r="I1132" t="str">
+        <v/>
+      </c>
+      <c r="J1132" t="str">
+        <v/>
+      </c>
+      <c r="K1132" t="str">
+        <v/>
+      </c>
+      <c r="L1132" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1133">
+      <c r="A1133" t="str">
+        <v/>
+      </c>
+      <c r="B1133" t="str">
+        <v>모녀한식뷔페인천</v>
+      </c>
+      <c r="C1133" t="str">
+        <v>남동구</v>
+      </c>
+      <c r="D1133" t="str">
+        <v>인천광역시 남동구 호구포로800번길 21-3</v>
+      </c>
+      <c r="E1133" t="str">
+        <v>37.453924</v>
+      </c>
+      <c r="F1133" t="str">
+        <v>126.720320</v>
+      </c>
+      <c r="G1133" t="str">
+        <v/>
+      </c>
+      <c r="H1133" t="str">
+        <v/>
+      </c>
+      <c r="I1133" t="str">
+        <v/>
+      </c>
+      <c r="J1133" t="str">
+        <v/>
+      </c>
+      <c r="K1133" t="str">
+        <v/>
+      </c>
+      <c r="L1133" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1134">
+      <c r="A1134" t="str">
+        <v/>
+      </c>
+      <c r="B1134" t="str">
+        <v>하르방</v>
+      </c>
+      <c r="C1134" t="str">
+        <v>남동구</v>
+      </c>
+      <c r="D1134" t="str">
+        <v>인천광역시 남동구 구월로276번길 39</v>
+      </c>
+      <c r="E1134" t="str">
+        <v>37.453836</v>
+      </c>
+      <c r="F1134" t="str">
+        <v>126.721338</v>
+      </c>
+      <c r="G1134" t="str">
+        <v/>
+      </c>
+      <c r="H1134" t="str">
+        <v/>
+      </c>
+      <c r="I1134" t="str">
+        <v/>
+      </c>
+      <c r="J1134" t="str">
+        <v/>
+      </c>
+      <c r="K1134" t="str">
+        <v/>
+      </c>
+      <c r="L1134" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1135">
+      <c r="A1135" t="str">
+        <v/>
+      </c>
+      <c r="B1135" t="str">
+        <v>왕의밥상한식뷔페</v>
+      </c>
+      <c r="C1135" t="str">
+        <v>남동구</v>
+      </c>
+      <c r="D1135" t="str">
+        <v>인천광역시 남동구 인하로 497-9</v>
+      </c>
+      <c r="E1135" t="str">
+        <v>37.444003</v>
+      </c>
+      <c r="F1135" t="str">
+        <v>126.701576</v>
+      </c>
+      <c r="G1135" t="str">
+        <v/>
+      </c>
+      <c r="H1135" t="str">
+        <v/>
+      </c>
+      <c r="I1135" t="str">
+        <v/>
+      </c>
+      <c r="J1135" t="str">
+        <v/>
+      </c>
+      <c r="K1135" t="str">
+        <v/>
+      </c>
+      <c r="L1135" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1136">
+      <c r="A1136" t="str">
+        <v/>
+      </c>
+      <c r="B1136" t="str">
+        <v>파티프라임부페</v>
+      </c>
+      <c r="C1136" t="str">
+        <v>미추홀구</v>
+      </c>
+      <c r="D1136" t="str">
+        <v>인천광역시 미추홀구 경원대로 869</v>
+      </c>
+      <c r="E1136" t="str">
+        <v>37.460387</v>
+      </c>
+      <c r="F1136" t="str">
+        <v>126.689134</v>
+      </c>
+      <c r="G1136" t="str">
+        <v/>
+      </c>
+      <c r="H1136" t="str">
+        <v/>
+      </c>
+      <c r="I1136" t="str">
+        <v/>
+      </c>
+      <c r="J1136" t="str">
+        <v/>
+      </c>
+      <c r="K1136" t="str">
+        <v/>
+      </c>
+      <c r="L1136" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1137">
+      <c r="A1137" t="str">
+        <v/>
+      </c>
+      <c r="B1137" t="str">
+        <v>미추홀도서관위탁급식소</v>
+      </c>
+      <c r="C1137" t="str">
+        <v>남동구</v>
+      </c>
+      <c r="D1137" t="str">
+        <v>인천광역시 남동구 인주대로776번길 53</v>
+      </c>
+      <c r="E1137" t="str">
+        <v>37.447051</v>
+      </c>
+      <c r="F1137" t="str">
+        <v>126.724866</v>
+      </c>
+      <c r="G1137" t="str">
+        <v/>
+      </c>
+      <c r="H1137" t="str">
+        <v/>
+      </c>
+      <c r="I1137" t="str">
+        <v/>
+      </c>
+      <c r="J1137" t="str">
+        <v/>
+      </c>
+      <c r="K1137" t="str">
+        <v/>
+      </c>
+      <c r="L1137" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1138">
+      <c r="A1138" t="str">
+        <v/>
+      </c>
+      <c r="B1138" t="str">
+        <v>대경푸드</v>
+      </c>
+      <c r="C1138" t="str">
+        <v>남동구</v>
+      </c>
+      <c r="D1138" t="str">
+        <v>인천광역시 남동구 인주대로 670</v>
+      </c>
+      <c r="E1138" t="str">
+        <v>37.449100</v>
+      </c>
+      <c r="F1138" t="str">
+        <v>126.711388</v>
+      </c>
+      <c r="G1138" t="str">
+        <v/>
+      </c>
+      <c r="H1138" t="str">
+        <v/>
+      </c>
+      <c r="I1138" t="str">
+        <v/>
+      </c>
+      <c r="J1138" t="str">
+        <v/>
+      </c>
+      <c r="K1138" t="str">
+        <v/>
+      </c>
+      <c r="L1138" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1139">
+      <c r="A1139" t="str">
+        <v/>
+      </c>
+      <c r="B1139" t="str">
+        <v>행복한한식뷔페</v>
+      </c>
+      <c r="C1139" t="str">
+        <v>미추홀구</v>
+      </c>
+      <c r="D1139" t="str">
+        <v>인천광역시 미추홀구 경인로 434</v>
+      </c>
+      <c r="E1139" t="str">
+        <v>37.457528</v>
+      </c>
+      <c r="F1139" t="str">
+        <v>126.688197</v>
+      </c>
+      <c r="G1139" t="str">
+        <v/>
+      </c>
+      <c r="H1139" t="str">
+        <v/>
+      </c>
+      <c r="I1139" t="str">
+        <v/>
+      </c>
+      <c r="J1139" t="str">
+        <v/>
+      </c>
+      <c r="K1139" t="str">
+        <v/>
+      </c>
+      <c r="L1139" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1140">
+      <c r="A1140" t="str">
+        <v/>
+      </c>
+      <c r="B1140" t="str">
+        <v>전주밥상한식부페</v>
+      </c>
+      <c r="C1140" t="str">
+        <v>남동구</v>
+      </c>
+      <c r="D1140" t="str">
+        <v>인천광역시 남동구 용천로115번길 4</v>
+      </c>
+      <c r="E1140" t="str">
+        <v>37.459946</v>
+      </c>
+      <c r="F1140" t="str">
+        <v>126.714466</v>
+      </c>
+      <c r="G1140" t="str">
+        <v/>
+      </c>
+      <c r="H1140" t="str">
+        <v/>
+      </c>
+      <c r="I1140" t="str">
+        <v/>
+      </c>
+      <c r="J1140" t="str">
+        <v/>
+      </c>
+      <c r="K1140" t="str">
+        <v/>
+      </c>
+      <c r="L1140" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1141">
+      <c r="A1141" t="str">
+        <v/>
+      </c>
+      <c r="B1141" t="str">
+        <v>쿠우쿠우구월동점</v>
+      </c>
+      <c r="C1141" t="str">
+        <v>남동구</v>
+      </c>
+      <c r="D1141" t="str">
+        <v>인천광역시 남동구 선수촌공원로 1</v>
+      </c>
+      <c r="E1141" t="str">
+        <v>37.439184</v>
+      </c>
+      <c r="F1141" t="str">
+        <v>126.709629</v>
+      </c>
+      <c r="G1141" t="str">
+        <v/>
+      </c>
+      <c r="H1141" t="str">
+        <v/>
+      </c>
+      <c r="I1141" t="str">
+        <v/>
+      </c>
+      <c r="J1141" t="str">
+        <v/>
+      </c>
+      <c r="K1141" t="str">
+        <v/>
+      </c>
+      <c r="L1141" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1142">
+      <c r="A1142" t="str">
+        <v/>
+      </c>
+      <c r="B1142" t="str">
+        <v>고향농원</v>
+      </c>
+      <c r="C1142" t="str">
+        <v>남동구</v>
+      </c>
+      <c r="D1142" t="str">
+        <v>인천광역시 남동구 덕골로 122</v>
+      </c>
+      <c r="E1142" t="str">
+        <v>37.429621</v>
+      </c>
+      <c r="F1142" t="str">
+        <v>126.723077</v>
+      </c>
+      <c r="G1142" t="str">
+        <v/>
+      </c>
+      <c r="H1142" t="str">
+        <v/>
+      </c>
+      <c r="I1142" t="str">
+        <v/>
+      </c>
+      <c r="J1142" t="str">
+        <v/>
+      </c>
+      <c r="K1142" t="str">
+        <v/>
+      </c>
+      <c r="L1142" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1143">
+      <c r="A1143" t="str">
+        <v/>
+      </c>
+      <c r="B1143" t="str">
+        <v>그린위치</v>
+      </c>
+      <c r="C1143" t="str">
+        <v>남동구</v>
+      </c>
+      <c r="D1143" t="str">
+        <v>인천광역시 남동구 미래로 21</v>
+      </c>
+      <c r="E1143" t="str">
+        <v>37.451884</v>
+      </c>
+      <c r="F1143" t="str">
+        <v>126.704088</v>
+      </c>
+      <c r="G1143" t="str">
+        <v/>
+      </c>
+      <c r="H1143" t="str">
+        <v/>
+      </c>
+      <c r="I1143" t="str">
+        <v/>
+      </c>
+      <c r="J1143" t="str">
+        <v/>
+      </c>
+      <c r="K1143" t="str">
+        <v/>
+      </c>
+      <c r="L1143" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1144">
+      <c r="A1144" t="str">
+        <v/>
+      </c>
+      <c r="B1144" t="str">
+        <v>엄마손한식부페</v>
+      </c>
+      <c r="C1144" t="str">
+        <v>남동구</v>
+      </c>
+      <c r="D1144" t="str">
+        <v>인천광역시 남동구 석산로 61</v>
+      </c>
+      <c r="E1144" t="str">
+        <v>37.460926</v>
+      </c>
+      <c r="F1144" t="str">
+        <v>126.698796</v>
+      </c>
+      <c r="G1144" t="str">
+        <v/>
+      </c>
+      <c r="H1144" t="str">
+        <v/>
+      </c>
+      <c r="I1144" t="str">
+        <v/>
+      </c>
+      <c r="J1144" t="str">
+        <v/>
+      </c>
+      <c r="K1144" t="str">
+        <v/>
+      </c>
+      <c r="L1144" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1145">
+      <c r="A1145" t="str">
+        <v/>
+      </c>
+      <c r="B1145" t="str">
+        <v>밥카페한식뷔페</v>
+      </c>
+      <c r="C1145" t="str">
+        <v>남동구</v>
+      </c>
+      <c r="D1145" t="str">
+        <v>인천광역시 남동구 복개서로97번길 37</v>
+      </c>
+      <c r="E1145" t="str">
+        <v>37.455321</v>
+      </c>
+      <c r="F1145" t="str">
+        <v>126.720428</v>
+      </c>
+      <c r="G1145" t="str">
+        <v/>
+      </c>
+      <c r="H1145" t="str">
+        <v/>
+      </c>
+      <c r="I1145" t="str">
+        <v/>
+      </c>
+      <c r="J1145" t="str">
+        <v/>
+      </c>
+      <c r="K1145" t="str">
+        <v/>
+      </c>
+      <c r="L1145" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1146">
+      <c r="A1146" t="str">
+        <v/>
+      </c>
+      <c r="B1146" t="str">
+        <v>부성한식부페</v>
+      </c>
+      <c r="C1146" t="str">
+        <v>남동구</v>
+      </c>
+      <c r="D1146" t="str">
+        <v>인천광역시 남동구 남동대로915번길 53</v>
+      </c>
+      <c r="E1146" t="str">
+        <v>37.464653</v>
+      </c>
+      <c r="F1146" t="str">
+        <v>126.704908</v>
+      </c>
+      <c r="G1146" t="str">
+        <v/>
+      </c>
+      <c r="H1146" t="str">
+        <v/>
+      </c>
+      <c r="I1146" t="str">
+        <v/>
+      </c>
+      <c r="J1146" t="str">
+        <v/>
+      </c>
+      <c r="K1146" t="str">
+        <v/>
+      </c>
+      <c r="L1146" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1147">
+      <c r="A1147" t="str">
+        <v/>
+      </c>
+      <c r="B1147" t="str">
+        <v>신선한식뷔페</v>
+      </c>
+      <c r="C1147" t="str">
+        <v>미추홀구</v>
+      </c>
+      <c r="D1147" t="str">
+        <v>인천광역시 미추홀구 경인로380번길 7-1</v>
+      </c>
+      <c r="E1147" t="str">
+        <v>37.457873</v>
+      </c>
+      <c r="F1147" t="str">
+        <v>126.682273</v>
+      </c>
+      <c r="G1147" t="str">
+        <v/>
+      </c>
+      <c r="H1147" t="str">
+        <v/>
+      </c>
+      <c r="I1147" t="str">
+        <v/>
+      </c>
+      <c r="J1147" t="str">
+        <v/>
+      </c>
+      <c r="K1147" t="str">
+        <v/>
+      </c>
+      <c r="L1147" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1148">
+      <c r="A1148" t="str">
+        <v/>
+      </c>
+      <c r="B1148" t="str">
+        <v>우리집뷔페</v>
+      </c>
+      <c r="C1148" t="str">
+        <v>남동구</v>
+      </c>
+      <c r="D1148" t="str">
+        <v>인천광역시 남동구 구월남로 150</v>
+      </c>
+      <c r="E1148" t="str">
+        <v>37.452799</v>
+      </c>
+      <c r="F1148" t="str">
+        <v>126.706152</v>
+      </c>
+      <c r="G1148" t="str">
+        <v/>
+      </c>
+      <c r="H1148" t="str">
+        <v/>
+      </c>
+      <c r="I1148" t="str">
+        <v/>
+      </c>
+      <c r="J1148" t="str">
+        <v/>
+      </c>
+      <c r="K1148" t="str">
+        <v/>
+      </c>
+      <c r="L1148" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1149">
+      <c r="A1149" t="str">
+        <v/>
+      </c>
+      <c r="B1149" t="str">
+        <v>호호상회</v>
+      </c>
+      <c r="C1149" t="str">
+        <v>미추홀구</v>
+      </c>
+      <c r="D1149" t="str">
+        <v>인천광역시 미추홀구 인하로 274-38</v>
+      </c>
+      <c r="E1149" t="str">
+        <v>37.447159</v>
+      </c>
+      <c r="F1149" t="str">
+        <v>126.678396</v>
+      </c>
+      <c r="G1149" t="str">
+        <v/>
+      </c>
+      <c r="H1149" t="str">
+        <v/>
+      </c>
+      <c r="I1149" t="str">
+        <v/>
+      </c>
+      <c r="J1149" t="str">
+        <v/>
+      </c>
+      <c r="K1149" t="str">
+        <v/>
+      </c>
+      <c r="L1149" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1150">
+      <c r="A1150" t="str">
+        <v/>
+      </c>
+      <c r="B1150" t="str">
+        <v>늘봄한식뷔페</v>
+      </c>
+      <c r="C1150" t="str">
+        <v>남동구</v>
+      </c>
+      <c r="D1150" t="str">
+        <v>인천광역시 남동구 남동대로915번길 3</v>
+      </c>
+      <c r="E1150" t="str">
+        <v>37.464210</v>
+      </c>
+      <c r="F1150" t="str">
+        <v>126.707724</v>
+      </c>
+      <c r="G1150" t="str">
+        <v/>
+      </c>
+      <c r="H1150" t="str">
+        <v/>
+      </c>
+      <c r="I1150" t="str">
+        <v/>
+      </c>
+      <c r="J1150" t="str">
+        <v/>
+      </c>
+      <c r="K1150" t="str">
+        <v/>
+      </c>
+      <c r="L1150" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1151">
+      <c r="A1151" t="str">
+        <v/>
+      </c>
+      <c r="B1151" t="str">
+        <v>모래내한식뷔페</v>
+      </c>
+      <c r="C1151" t="str">
+        <v>남동구</v>
+      </c>
+      <c r="D1151" t="str">
+        <v>인천광역시 남동구 복개서로97번길 37</v>
+      </c>
+      <c r="E1151" t="str">
+        <v>37.455321</v>
+      </c>
+      <c r="F1151" t="str">
+        <v>126.720428</v>
+      </c>
+      <c r="G1151" t="str">
+        <v/>
+      </c>
+      <c r="H1151" t="str">
+        <v/>
+      </c>
+      <c r="I1151" t="str">
+        <v/>
+      </c>
+      <c r="J1151" t="str">
+        <v/>
+      </c>
+      <c r="K1151" t="str">
+        <v/>
+      </c>
+      <c r="L1151" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1152">
+      <c r="A1152" t="str">
+        <v/>
+      </c>
+      <c r="B1152" t="str">
+        <v>동원홈푸드인천지방국세청</v>
+      </c>
+      <c r="C1152" t="str">
+        <v>남동구</v>
+      </c>
+      <c r="D1152" t="str">
+        <v>인천광역시 남동구 남동대로 764</v>
+      </c>
+      <c r="E1152" t="str">
+        <v>37.450443</v>
+      </c>
+      <c r="F1152" t="str">
+        <v>126.708094</v>
+      </c>
+      <c r="G1152" t="str">
+        <v/>
+      </c>
+      <c r="H1152" t="str">
+        <v/>
+      </c>
+      <c r="I1152" t="str">
+        <v/>
+      </c>
+      <c r="J1152" t="str">
+        <v/>
+      </c>
+      <c r="K1152" t="str">
+        <v/>
+      </c>
+      <c r="L1152" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1153">
+      <c r="A1153" t="str">
+        <v/>
+      </c>
+      <c r="B1153" t="str">
+        <v>대홍싸브싸브부페</v>
+      </c>
+      <c r="C1153" t="str">
+        <v>남동구</v>
+      </c>
+      <c r="D1153" t="str">
+        <v>인천광역시 남동구 문화서로18번길 2</v>
+      </c>
+      <c r="E1153" t="str">
+        <v>37.446827</v>
+      </c>
+      <c r="F1153" t="str">
+        <v>126.696140</v>
+      </c>
+      <c r="G1153" t="str">
+        <v/>
+      </c>
+      <c r="H1153" t="str">
+        <v/>
+      </c>
+      <c r="I1153" t="str">
+        <v/>
+      </c>
+      <c r="J1153" t="str">
+        <v/>
+      </c>
+      <c r="K1153" t="str">
+        <v/>
+      </c>
+      <c r="L1153" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1154">
+      <c r="A1154" t="str">
+        <v/>
+      </c>
+      <c r="B1154" t="str">
+        <v>아워홈SSG랜더스문학</v>
+      </c>
+      <c r="C1154" t="str">
+        <v>미추홀구</v>
+      </c>
+      <c r="D1154" t="str">
+        <v>인천광역시 미추홀구 매소홀로 618</v>
+      </c>
+      <c r="E1154" t="str">
+        <v>37.435082</v>
+      </c>
+      <c r="F1154" t="str">
+        <v>126.690787</v>
+      </c>
+      <c r="G1154" t="str">
+        <v/>
+      </c>
+      <c r="H1154" t="str">
+        <v/>
+      </c>
+      <c r="I1154" t="str">
+        <v/>
+      </c>
+      <c r="J1154" t="str">
+        <v/>
+      </c>
+      <c r="K1154" t="str">
+        <v/>
+      </c>
+      <c r="L1154" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1155">
+      <c r="A1155" t="str">
+        <v/>
+      </c>
+      <c r="B1155" t="str">
+        <v>조은밥상한식뷔페</v>
+      </c>
+      <c r="C1155" t="str">
+        <v>남동구</v>
+      </c>
+      <c r="D1155" t="str">
+        <v>인천광역시 남동구 성말로13번길 15</v>
+      </c>
+      <c r="E1155" t="str">
+        <v>37.446265</v>
+      </c>
+      <c r="F1155" t="str">
+        <v>126.701793</v>
+      </c>
+      <c r="G1155" t="str">
+        <v/>
+      </c>
+      <c r="H1155" t="str">
+        <v/>
+      </c>
+      <c r="I1155" t="str">
+        <v/>
+      </c>
+      <c r="J1155" t="str">
+        <v/>
+      </c>
+      <c r="K1155" t="str">
+        <v/>
+      </c>
+      <c r="L1155" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1156">
+      <c r="A1156" t="str">
+        <v/>
+      </c>
+      <c r="B1156" t="str">
+        <v>자매식당</v>
+      </c>
+      <c r="C1156" t="str">
+        <v>남동구</v>
+      </c>
+      <c r="D1156" t="str">
+        <v>인천광역시 남동구 구월말로 67</v>
+      </c>
+      <c r="E1156" t="str">
+        <v>37.455079</v>
+      </c>
+      <c r="F1156" t="str">
+        <v>126.724860</v>
+      </c>
+      <c r="G1156" t="str">
+        <v/>
+      </c>
+      <c r="H1156" t="str">
+        <v/>
+      </c>
+      <c r="I1156" t="str">
+        <v/>
+      </c>
+      <c r="J1156" t="str">
+        <v/>
+      </c>
+      <c r="K1156" t="str">
+        <v/>
+      </c>
+      <c r="L1156" t="str">
+        <v/>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L1008"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L1156"/>
   </ignoredErrors>
 </worksheet>
 </file>